--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -2229,17 +2229,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2281,426 +2281,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-05T11:22:16Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -53,7 +53,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FFC000"/>
     </font>
     <font>
       <b val="1"/>
@@ -61,7 +61,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFC000"/>
+      <color rgb="0000E676"/>
     </font>
   </fonts>
   <fills count="5">
@@ -517,10 +517,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -539,7 +539,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>March 2026 - April 2026 Shoe Releases</t>
+          <t>March 2026 Shoe Releases</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -644,15 +644,19 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -660,12 +664,12 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr"/>
@@ -674,12 +678,12 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -694,15 +698,19 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -710,12 +718,12 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr"/>
@@ -724,10 +732,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -749,7 +757,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -764,12 +772,12 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr"/>
@@ -778,10 +786,10 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -803,12 +811,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro, exclusive</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -818,7 +826,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
@@ -832,10 +840,10 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -882,12 +890,12 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -907,12 +915,12 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -927,7 +935,7 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr"/>
@@ -936,10 +944,10 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -961,14 +969,10 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -981,7 +985,7 @@
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr"/>
@@ -990,12 +994,12 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1015,10 +1019,14 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1031,7 +1039,7 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr"/>
@@ -1040,10 +1048,10 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46088</v>
+        <v>46091</v>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1060,17 +1068,17 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -1085,7 +1093,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr"/>
@@ -1094,10 +1102,10 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1119,12 +1127,12 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1139,7 +1147,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr"/>
@@ -1151,7 +1159,7 @@
         <v>46095</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1173,7 +1181,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -1199,164 +1207,6 @@
       <c r="L14" s="10" t="inlineStr"/>
       <c r="M14" s="10" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1373,10 +1223,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1395,7 +1245,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>March 2026 - April 2026 Shoe Releases</t>
+          <t>March 2026 Shoe Releases</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1330,12 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1500,15 +1350,19 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1516,12 +1370,12 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr"/>
@@ -1530,12 +1384,12 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -1550,15 +1404,19 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1566,12 +1424,12 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr"/>
@@ -1580,10 +1438,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1605,7 +1463,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1620,12 +1478,12 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr"/>
@@ -1634,10 +1492,10 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1659,12 +1517,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro, exclusive</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1674,7 +1532,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
@@ -1688,10 +1546,10 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1738,12 +1596,12 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1763,12 +1621,12 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1783,7 +1641,7 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr"/>
@@ -1792,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1817,14 +1675,10 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1837,7 +1691,7 @@
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr"/>
@@ -1846,12 +1700,12 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1871,10 +1725,14 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1887,7 +1745,7 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr"/>
@@ -1896,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46088</v>
+        <v>46091</v>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1916,17 +1774,17 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -1941,7 +1799,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr"/>
@@ -1950,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1975,12 +1833,12 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1995,7 +1853,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr"/>
@@ -2007,7 +1865,7 @@
         <v>46095</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2029,7 +1887,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -2055,164 +1913,6 @@
       <c r="L14" s="10" t="inlineStr"/>
       <c r="M14" s="10" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2229,17 +1929,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2281,6 +1981,516 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Neon Yellow</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-06T05:03:21Z</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2400,14 +2610,14 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2422,15 +2632,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2438,18 +2652,18 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="O2" t="n">
         <v>50</v>
@@ -2458,14 +2672,14 @@
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2480,15 +2694,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2496,18 +2714,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="O3" t="n">
         <v>50</v>
@@ -2516,7 +2734,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -2543,7 +2761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2558,12 +2776,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -2578,7 +2796,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -2605,12 +2823,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro, exclusive</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2620,7 +2838,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2640,7 +2858,7 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -2698,14 +2916,14 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2725,12 +2943,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2745,13 +2963,13 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-og-neon-yellow1</t>
+          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>50</v>
@@ -2760,7 +2978,7 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -2787,14 +3005,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike SB Ishod Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2807,7 +3021,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -2822,14 +3036,14 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2849,10 +3063,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Zoom Vomero 5 Hyper Royal</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2865,13 +3083,13 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O9" t="n">
         <v>50</v>
@@ -2880,7 +3098,7 @@
     </row>
     <row r="10">
       <c r="A10" s="13" t="n">
-        <v>46088</v>
+        <v>46091</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -2902,17 +3120,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2927,7 +3145,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>/launch/t/womens-air-jordan-1-high-og-psychic-blue-and-pale-ivory</t>
+          <t>/launch/t/zoom-vomero-5-hyper-royal</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -2942,7 +3160,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -2969,12 +3187,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2989,13 +3207,13 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
         <v>50</v>
@@ -3031,7 +3249,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3063,188 +3281,6 @@
         <v>50</v>
       </c>
       <c r="P12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Mar 14 Shoes Air Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>22</v>
-      </c>
-      <c r="O13" t="n">
-        <v>50</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>12</v>
-      </c>
-      <c r="O14" t="n">
-        <v>50</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>12</v>
-      </c>
-      <c r="O15" t="n">
-        <v>50</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3369,7 +3405,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="12" t="n"/>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="9" t="n"/>
@@ -3419,7 +3455,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3429,7 +3465,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5"/>
@@ -3457,7 +3493,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3467,7 +3503,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10"/>
@@ -3495,7 +3531,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -3505,7 +3541,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15"/>
@@ -3533,7 +3569,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -57,7 +57,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007CFCFF"/>
+      <color rgb="00FFD966"/>
     </font>
     <font>
       <b val="1"/>
@@ -65,7 +65,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFD966"/>
+      <color rgb="007CFCFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -643,9 +643,7 @@
       <c r="A4" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -653,7 +651,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -698,9 +696,7 @@
       <c r="A5" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -708,7 +704,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -759,7 +755,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -810,9 +806,7 @@
       <c r="A7" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -820,12 +814,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -869,9 +863,7 @@
       <c r="A8" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -879,12 +871,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -928,9 +920,7 @@
       <c r="A9" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -938,7 +928,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -987,15 +977,13 @@
       <c r="A10" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1046,15 +1034,13 @@
       <c r="A11" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1105,9 +1091,7 @@
       <c r="A12" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1115,7 +1099,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1160,9 +1144,7 @@
       <c r="A13" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1170,7 +1152,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1215,9 +1197,7 @@
       <c r="A14" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1225,7 +1205,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1270,9 +1250,7 @@
       <c r="A15" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1280,7 +1258,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1325,9 +1303,7 @@
       <c r="A16" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1335,7 +1311,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1380,9 +1356,7 @@
       <c r="A17" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1390,7 +1364,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1435,9 +1409,7 @@
       <c r="A18" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -1445,12 +1417,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1500,7 +1472,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1551,9 +1523,7 @@
       <c r="A20" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1561,7 +1531,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1610,9 +1580,7 @@
       <c r="A21" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1620,7 +1588,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1665,9 +1633,7 @@
       <c r="A22" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -1675,12 +1641,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -1730,7 +1696,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1781,9 +1747,7 @@
       <c r="A24" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -1791,12 +1755,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -1840,9 +1804,7 @@
       <c r="A25" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1850,7 +1812,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1895,15 +1857,13 @@
       <c r="A26" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1950,9 +1910,7 @@
       <c r="A27" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1960,7 +1918,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -2009,9 +1967,7 @@
       <c r="A28" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2019,7 +1975,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -2068,15 +2024,13 @@
       <c r="A29" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2123,9 +2077,7 @@
       <c r="A30" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2133,7 +2085,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -2188,7 +2140,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2239,9 +2191,7 @@
       <c r="A32" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2249,7 +2199,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -2294,15 +2244,13 @@
       <c r="A33" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2349,9 +2297,7 @@
       <c r="A34" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>25</v>
-      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2359,7 +2305,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -2410,7 +2356,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2463,7 +2409,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2516,7 +2462,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2573,7 +2519,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2630,7 +2576,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2687,7 +2633,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2744,7 +2690,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2801,7 +2747,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2858,7 +2804,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2915,7 +2861,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2972,7 +2918,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3029,7 +2975,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3086,7 +3032,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3143,7 +3089,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3196,7 +3142,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3253,7 +3199,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3310,7 +3256,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3367,7 +3313,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3424,7 +3370,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3477,7 +3423,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3534,7 +3480,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3587,7 +3533,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3640,7 +3586,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3697,7 +3643,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3754,7 +3700,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3811,7 +3757,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3864,7 +3810,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3917,7 +3863,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3974,7 +3920,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4027,7 +3973,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4084,7 +4030,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4141,7 +4087,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4198,7 +4144,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4255,7 +4201,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4312,7 +4258,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4365,7 +4311,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4422,7 +4368,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4479,7 +4425,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4532,7 +4478,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4589,7 +4535,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4642,7 +4588,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4695,7 +4641,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4748,7 +4694,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4801,7 +4747,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4854,7 +4800,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4911,7 +4857,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4964,7 +4910,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5017,7 +4963,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5070,7 +5016,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5127,7 +5073,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5180,7 +5126,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5237,7 +5183,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5294,7 +5240,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5351,7 +5297,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5408,7 +5354,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5465,7 +5411,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5518,7 +5464,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5571,7 +5517,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5628,7 +5574,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5681,7 +5627,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5734,7 +5680,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5791,7 +5737,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -5844,7 +5790,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5897,7 +5843,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -6074,9 +6020,7 @@
       <c r="A4" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6084,7 +6028,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -6129,9 +6073,7 @@
       <c r="A5" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6139,7 +6081,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -6190,7 +6132,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -6241,9 +6183,7 @@
       <c r="A7" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6251,12 +6191,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -6300,9 +6240,7 @@
       <c r="A8" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6310,12 +6248,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -6359,9 +6297,7 @@
       <c r="A9" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6369,7 +6305,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -6418,15 +6354,13 @@
       <c r="A10" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6477,15 +6411,13 @@
       <c r="A11" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -6536,9 +6468,7 @@
       <c r="A12" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6546,7 +6476,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -6591,9 +6521,7 @@
       <c r="A13" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6601,7 +6529,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -6646,9 +6574,7 @@
       <c r="A14" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6656,7 +6582,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -6701,9 +6627,7 @@
       <c r="A15" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6711,7 +6635,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -6756,9 +6680,7 @@
       <c r="A16" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6766,7 +6688,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -6811,9 +6733,7 @@
       <c r="A17" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6821,7 +6741,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -6866,9 +6786,7 @@
       <c r="A18" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6876,12 +6794,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -6931,7 +6849,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -6982,9 +6900,7 @@
       <c r="A20" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -6992,7 +6908,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -7041,9 +6957,7 @@
       <c r="A21" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7051,7 +6965,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -7096,9 +7010,7 @@
       <c r="A22" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -7106,12 +7018,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -7161,7 +7073,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7212,9 +7124,7 @@
       <c r="A24" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -7222,12 +7132,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -7271,9 +7181,7 @@
       <c r="A25" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7281,7 +7189,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -7326,15 +7234,13 @@
       <c r="A26" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -7381,9 +7287,7 @@
       <c r="A27" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7391,7 +7295,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -7440,9 +7344,7 @@
       <c r="A28" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7450,7 +7352,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -7499,15 +7401,13 @@
       <c r="A29" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -7554,9 +7454,7 @@
       <c r="A30" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7564,7 +7462,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -7619,7 +7517,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7670,9 +7568,7 @@
       <c r="A32" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7680,7 +7576,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -7725,15 +7621,13 @@
       <c r="A33" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>180</v>
-      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -7780,9 +7674,7 @@
       <c r="A34" s="4" t="n">
         <v>46087</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>25</v>
-      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7790,7 +7682,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -7841,7 +7733,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7894,7 +7786,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7947,7 +7839,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8004,7 +7896,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8061,7 +7953,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8118,7 +8010,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8175,7 +8067,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8232,7 +8124,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8289,7 +8181,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8346,7 +8238,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8403,7 +8295,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8460,7 +8352,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8517,7 +8409,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8574,7 +8466,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8627,7 +8519,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8684,7 +8576,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8741,7 +8633,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8798,7 +8690,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8855,7 +8747,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8908,7 +8800,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8965,7 +8857,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9018,7 +8910,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9071,7 +8963,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9128,7 +9020,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9185,7 +9077,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9242,7 +9134,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9295,7 +9187,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9348,7 +9240,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9405,7 +9297,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9458,7 +9350,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9515,7 +9407,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9572,7 +9464,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9629,7 +9521,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9686,7 +9578,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9743,7 +9635,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9796,7 +9688,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9853,7 +9745,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9910,7 +9802,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -9963,7 +9855,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10020,7 +9912,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10073,7 +9965,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10126,7 +10018,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10179,7 +10071,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10232,7 +10124,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10285,7 +10177,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10342,7 +10234,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10395,7 +10287,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10448,7 +10340,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10501,7 +10393,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10558,7 +10450,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10611,7 +10503,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10668,7 +10560,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10725,7 +10617,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10782,7 +10674,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -10839,7 +10731,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10896,7 +10788,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D90" s="12" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -10949,7 +10841,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11002,7 +10894,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11059,7 +10951,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11112,7 +11004,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11165,7 +11057,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11222,7 +11114,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -11275,7 +11167,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11328,7 +11220,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -11390,7 +11282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11398,8 +11290,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -11473,17 +11365,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11515,17 +11407,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11557,17 +11449,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11599,17 +11491,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11641,17 +11533,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11683,17 +11575,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11725,17 +11617,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11767,17 +11659,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11809,17 +11701,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11851,17 +11743,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11785,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11827,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -11977,17 +11869,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12019,17 +11911,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12061,17 +11953,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12103,17 +11995,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12145,17 +12037,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12187,17 +12079,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12229,17 +12121,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12271,17 +12163,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12313,17 +12205,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12355,17 +12247,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12397,17 +12289,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12439,17 +12331,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12481,17 +12373,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12523,17 +12415,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12565,17 +12457,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12607,17 +12499,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12649,17 +12541,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12691,17 +12583,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12733,17 +12625,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12775,17 +12667,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12817,17 +12709,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12859,17 +12751,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12793,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12943,17 +12835,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -12985,17 +12877,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13027,17 +12919,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13069,17 +12961,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13111,17 +13003,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13153,17 +13045,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13195,17 +13087,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13237,17 +13129,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13279,17 +13171,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13213,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13363,17 +13255,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13405,17 +13297,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13447,17 +13339,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13489,17 +13381,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13531,17 +13423,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13573,17 +13465,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13615,17 +13507,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13657,17 +13549,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13699,47 +13591,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-06T08:53:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-06T08:53:02Z</t>
+          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13730,7 @@
         <v>46087</v>
       </c>
       <c r="B2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13877,7 +13739,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13920,7 +13782,7 @@
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
@@ -13929,7 +13791,7 @@
         <v>46087</v>
       </c>
       <c r="B3" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -13938,7 +13800,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13981,7 +13843,7 @@
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -14055,7 +13917,7 @@
         <v>46087</v>
       </c>
       <c r="B5" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -14064,12 +13926,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -14111,7 +13973,7 @@
         <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -14120,7 +13982,7 @@
         <v>46087</v>
       </c>
       <c r="B6" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -14129,12 +13991,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -14176,7 +14038,7 @@
         <v>22</v>
       </c>
       <c r="P6" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -14185,7 +14047,7 @@
         <v>46087</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -14194,7 +14056,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -14241,7 +14103,7 @@
         <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -14250,7 +14112,7 @@
         <v>46087</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -14306,7 +14168,7 @@
         <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -14315,7 +14177,7 @@
         <v>46087</v>
       </c>
       <c r="B9" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -14371,7 +14233,7 @@
         <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -14380,7 +14242,7 @@
         <v>46087</v>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -14389,7 +14251,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -14432,7 +14294,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -14441,7 +14303,7 @@
         <v>46087</v>
       </c>
       <c r="B11" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -14450,7 +14312,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -14493,7 +14355,7 @@
         <v>12</v>
       </c>
       <c r="P11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -14502,7 +14364,7 @@
         <v>46087</v>
       </c>
       <c r="B12" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -14511,7 +14373,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -14554,7 +14416,7 @@
         <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
@@ -14563,7 +14425,7 @@
         <v>46087</v>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -14572,7 +14434,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -14615,7 +14477,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
@@ -14624,7 +14486,7 @@
         <v>46087</v>
       </c>
       <c r="B14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -14633,7 +14495,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -14676,7 +14538,7 @@
         <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -14685,7 +14547,7 @@
         <v>46087</v>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -14694,7 +14556,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -14737,7 +14599,7 @@
         <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -14746,7 +14608,7 @@
         <v>46087</v>
       </c>
       <c r="B16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -14755,12 +14617,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -14802,7 +14664,7 @@
         <v>22</v>
       </c>
       <c r="P16" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -14876,7 +14738,7 @@
         <v>46087</v>
       </c>
       <c r="B18" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -14885,7 +14747,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14932,7 +14794,7 @@
         <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -14941,7 +14803,7 @@
         <v>46087</v>
       </c>
       <c r="B19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -14950,7 +14812,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -14993,7 +14855,7 @@
         <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
@@ -15002,7 +14864,7 @@
         <v>46087</v>
       </c>
       <c r="B20" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -15011,12 +14873,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -15058,7 +14920,7 @@
         <v>22</v>
       </c>
       <c r="P20" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -15132,7 +14994,7 @@
         <v>46087</v>
       </c>
       <c r="B22" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -15141,12 +15003,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -15188,7 +15050,7 @@
         <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -15197,7 +15059,7 @@
         <v>46087</v>
       </c>
       <c r="B23" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -15206,7 +15068,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -15249,7 +15111,7 @@
         <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -15258,7 +15120,7 @@
         <v>46087</v>
       </c>
       <c r="B24" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -15310,7 +15172,7 @@
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -15319,7 +15181,7 @@
         <v>46087</v>
       </c>
       <c r="B25" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -15328,7 +15190,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -15375,7 +15237,7 @@
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -15384,7 +15246,7 @@
         <v>46087</v>
       </c>
       <c r="B26" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -15393,7 +15255,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -15440,7 +15302,7 @@
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -15449,7 +15311,7 @@
         <v>46087</v>
       </c>
       <c r="B27" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -15501,7 +15363,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -15510,7 +15372,7 @@
         <v>46087</v>
       </c>
       <c r="B28" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -15519,7 +15381,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -15566,7 +15428,7 @@
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -15640,7 +15502,7 @@
         <v>46087</v>
       </c>
       <c r="B30" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -15649,7 +15511,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -15692,7 +15554,7 @@
         <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -15701,7 +15563,7 @@
         <v>46087</v>
       </c>
       <c r="B31" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -15753,7 +15615,7 @@
         <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -15762,7 +15624,7 @@
         <v>46087</v>
       </c>
       <c r="B32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -15771,7 +15633,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -15811,10 +15673,10 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -20228,7 +20090,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -20238,7 +20100,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -11294,17 +11294,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11346,6 +11346,132 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Adidas Anthony Edwards 2 Georgia Bulldogs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-06T09:39:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Air Jordan 1 High OG Pale Ivory / Psychic Blue</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-06T09:39:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 OG Lakers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-06T09:39:05Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-grey-matter-u20004jq/705427</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-dark-team-red-patent-leather-pack-io4489-601/706787</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr"/>
@@ -714,12 +714,12 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-ice-wine-u20002t8/705920</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-mystic-navy-patent-leather-pack-io4489-400/706786</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr"/>
@@ -772,14 +772,10 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -795,7 +791,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-vomero-premium-black-iq0627-001/705450</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-topaz-gold-patent-leather-pack-io4489-700/706785</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -1198,9 +1194,9 @@
         <v>46093</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1220,12 +1216,12 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -1243,7 +1239,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -1260,9 +1256,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1277,7 +1273,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -1296,11 +1292,11 @@
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -1317,9 +1313,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1334,26 +1330,30 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -1382,23 +1382,23 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K17" s="9" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
+          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
+          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -1541,23 +1541,23 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Converse Shai 001 Pink</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr"/>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K20" s="9" t="n">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -1576,7 +1576,9 @@
       <c r="A21" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n">
+        <v>288</v>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -1599,18 +1601,18 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Converse Shai 001 Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K21" s="9" t="n">
@@ -1618,7 +1620,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
+          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -1635,9 +1637,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1652,30 +1654,26 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -1692,9 +1690,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -1704,12 +1702,12 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -1728,11 +1726,11 @@
         </is>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -1761,23 +1759,27 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K24" s="9" t="n">
@@ -1785,7 +1787,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -1819,7 +1821,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr"/>
@@ -1838,7 +1840,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -1855,9 +1857,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -1872,26 +1874,26 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 Faded Black / Utility Green</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -1908,9 +1910,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -1925,26 +1927,26 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>New Balance 1890 Faded Black / Utility Green</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -1956,9 +1958,9 @@
         <v>46093</v>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1973,27 +1975,23 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr"/>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K28" s="9" t="n">
@@ -2001,7 +1999,7 @@
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr"/>
@@ -2018,14 +2016,14 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -2035,30 +2033,30 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -2070,19 +2068,19 @@
         <v>46093</v>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -2092,26 +2090,30 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Kobe 3 Low Protro Pink Quartz</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -2145,7 +2147,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr"/>
@@ -2164,7 +2166,7 @@
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -2198,18 +2200,18 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -2217,7 +2219,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -4460,7 +4462,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
@@ -6111,7 +6113,7 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B104" s="5" t="inlineStr"/>
       <c r="C104" s="6" t="inlineStr">
@@ -6131,12 +6133,12 @@
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr"/>
@@ -6155,7 +6157,7 @@
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-team-usa-iq0407-100/706740</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr"/>
@@ -6164,12 +6166,12 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B105" s="5" t="inlineStr"/>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -6184,15 +6186,19 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H105" s="10" t="inlineStr"/>
+          <t>Nike Air Max 95 SE 'England'</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -6208,7 +6214,7 @@
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-se-england-iq0176-100/706661</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr"/>
@@ -6217,12 +6223,12 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B106" s="5" t="inlineStr"/>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -6242,12 +6248,12 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
@@ -6265,7 +6271,7 @@
       </c>
       <c r="L106" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-plus-french-football-federation-iq0170-400/706739</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr"/>
@@ -6294,12 +6300,12 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr"/>
@@ -6318,7 +6324,7 @@
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr"/>
@@ -6330,9 +6336,9 @@
         <v>46107</v>
       </c>
       <c r="B108" s="5" t="inlineStr"/>
-      <c r="C108" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -6347,19 +6353,15 @@
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
-        </is>
-      </c>
-      <c r="H108" s="10" t="inlineStr">
-        <is>
-          <t>collab, running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr"/>
       <c r="I108" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -6375,7 +6377,7 @@
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr"/>
@@ -6384,12 +6386,12 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B109" s="5" t="inlineStr"/>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -6409,18 +6411,22 @@
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr"/>
+          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K109" s="9" t="n">
@@ -6428,7 +6434,7 @@
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr"/>
@@ -6437,7 +6443,7 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B110" s="5" t="inlineStr"/>
       <c r="C110" s="6" t="inlineStr">
@@ -6462,7 +6468,7 @@
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr"/>
@@ -6481,12 +6487,122 @@
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr"/>
       <c r="N110" s="10" t="inlineStr"/>
       <c r="O110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr"/>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>collab, running, exclusive</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+        </is>
+      </c>
+      <c r="M111" s="10" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
+      <c r="O111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr"/>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr"/>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M112" s="10" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
+      <c r="O112" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6503,7 +6619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -6636,12 +6752,12 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr"/>
@@ -6660,7 +6776,7 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-grey-matter-u20004jq/705427</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-dark-team-red-patent-leather-pack-io4489-601/706787</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr"/>
@@ -6689,12 +6805,12 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr"/>
@@ -6713,7 +6829,7 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-ice-wine-u20002t8/705920</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-mystic-navy-patent-leather-pack-io4489-400/706786</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr"/>
@@ -6747,14 +6863,10 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -6770,7 +6882,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-vomero-premium-black-iq0627-001/705450</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-topaz-gold-patent-leather-pack-io4489-700/706785</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -7173,9 +7285,9 @@
         <v>46093</v>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -7195,12 +7307,12 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -7218,7 +7330,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -7235,9 +7347,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -7252,7 +7364,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -7271,11 +7383,11 @@
         </is>
       </c>
       <c r="K15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -7292,9 +7404,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -7309,26 +7421,30 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -7357,23 +7473,23 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K17" s="9" t="n">
@@ -7381,7 +7497,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
+          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -7415,7 +7531,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
+          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -7434,7 +7550,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -7468,7 +7584,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr"/>
@@ -7487,7 +7603,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -7516,23 +7632,23 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Converse Shai 001 Pink</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr"/>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K20" s="9" t="n">
@@ -7540,7 +7656,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -7551,7 +7667,9 @@
       <c r="A21" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n">
+        <v>288</v>
+      </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7574,18 +7692,18 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Converse Shai 001 Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K21" s="9" t="n">
@@ -7593,7 +7711,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
+          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -7610,9 +7728,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -7627,30 +7745,26 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -7667,9 +7781,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -7679,12 +7793,12 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -7703,11 +7817,11 @@
         </is>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -7736,23 +7850,27 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K24" s="9" t="n">
@@ -7760,7 +7878,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -7794,7 +7912,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr"/>
@@ -7813,7 +7931,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -7830,9 +7948,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -7847,26 +7965,26 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 Faded Black / Utility Green</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -7883,9 +8001,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -7900,26 +8018,26 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>New Balance 1890 Faded Black / Utility Green</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -7931,9 +8049,9 @@
         <v>46093</v>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -7948,27 +8066,23 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr"/>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K28" s="9" t="n">
@@ -7976,7 +8090,7 @@
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr"/>
@@ -7993,14 +8107,14 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -8010,30 +8124,30 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -8045,19 +8159,19 @@
         <v>46093</v>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -8067,26 +8181,30 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Kobe 3 Low Protro Pink Quartz</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -8120,7 +8238,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr"/>
@@ -8139,7 +8257,7 @@
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -8173,18 +8291,18 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr"/>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -8192,7 +8310,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -10435,7 +10553,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
@@ -12086,7 +12204,7 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B104" s="5" t="inlineStr"/>
       <c r="C104" s="6" t="inlineStr">
@@ -12106,12 +12224,12 @@
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr"/>
@@ -12130,7 +12248,7 @@
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-team-usa-iq0407-100/706740</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr"/>
@@ -12139,12 +12257,12 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B105" s="5" t="inlineStr"/>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -12159,15 +12277,19 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H105" s="10" t="inlineStr"/>
+          <t>Nike Air Max 95 SE 'England'</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -12183,7 +12305,7 @@
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-se-england-iq0176-100/706661</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr"/>
@@ -12192,12 +12314,12 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B106" s="5" t="inlineStr"/>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -12217,12 +12339,12 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
@@ -12240,7 +12362,7 @@
       </c>
       <c r="L106" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-plus-french-football-federation-iq0170-400/706739</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr"/>
@@ -12269,12 +12391,12 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr"/>
@@ -12293,7 +12415,7 @@
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr"/>
@@ -12305,9 +12427,9 @@
         <v>46107</v>
       </c>
       <c r="B108" s="5" t="inlineStr"/>
-      <c r="C108" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -12322,19 +12444,15 @@
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
-        </is>
-      </c>
-      <c r="H108" s="10" t="inlineStr">
-        <is>
-          <t>collab, running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr"/>
       <c r="I108" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -12350,7 +12468,7 @@
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr"/>
@@ -12359,12 +12477,12 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B109" s="5" t="inlineStr"/>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -12384,18 +12502,22 @@
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr"/>
+          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K109" s="9" t="n">
@@ -12403,7 +12525,7 @@
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr"/>
@@ -12412,7 +12534,7 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B110" s="5" t="inlineStr"/>
       <c r="C110" s="6" t="inlineStr">
@@ -12437,7 +12559,7 @@
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr"/>
@@ -12456,12 +12578,122 @@
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr"/>
       <c r="N110" s="10" t="inlineStr"/>
       <c r="O110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr"/>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>collab, running, exclusive</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+        </is>
+      </c>
+      <c r="M111" s="10" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
+      <c r="O111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr"/>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr"/>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M112" s="10" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
+      <c r="O112" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12478,13 +12710,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -12536,12 +12768,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12551,7 +12783,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -12559,14 +12791,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12576,12 +12808,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -12589,14 +12821,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12606,12 +12838,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -12619,7 +12851,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12636,12 +12868,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -12649,7 +12881,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12898,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -12679,7 +12911,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12696,12 +12928,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>Nike Vomero Premium 'Black' From £ 200</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -12709,29 +12941,29 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -12739,14 +12971,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12756,12 +12988,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -12769,14 +13001,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12786,32 +13018,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Nike Sabrina 3 Oregon Ducks</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12821,27 +13065,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>Air Jordan 13 Chicago</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12851,15 +13107,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>Air Jordan 1 Low OG Sail / Off White</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12871,17 +13139,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -12889,7 +13157,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12901,17 +13169,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>Nike Air Max 95 SE 'England'</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -12919,7 +13187,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -12931,7 +13199,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12941,7 +13209,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -12949,19 +13217,19 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RETAIL_CHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12971,351 +13239,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 Oregon Ducks</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Converse Kentucky Wildcats 30th Anniversary</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Reebok Angel Navy Halo</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Chicago</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG Sail / Off White</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nike GT Future Unseen Hours</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nike G.t. Cut 1 Orange Pulse / Persian Violet</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike G.t. Future Unseen Hours</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-11T06:09:39Z</t>
+          <t>2026-03-11T18:12:15Z</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q108"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13463,12 +13395,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Dark Team Red' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -13487,13 +13419,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-grey-matter-u20004jq/705427</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-dark-team-red-patent-leather-pack-io4489-601/706787</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>50</v>
@@ -13524,12 +13456,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
+          <t>Nike Air Force 1 Low 'Mystic Navy' - Patent Leather Pack From £ 110</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -13548,13 +13480,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-abzorb-2000-ice-wine-u20002t8/705920</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-mystic-navy-patent-leather-pack-io4489-400/706786</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
         <v>50</v>
@@ -13590,14 +13522,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Force 1 Low 'Topaz Gold' - Patent Leather Pack From £ 110</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -13613,7 +13541,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-vomero-premium-black-iq0627-001/705450</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-topaz-gold-patent-leather-pack-io4489-700/706785</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -14082,7 +14010,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -14102,12 +14030,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -14125,13 +14053,13 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P12" t="n">
         <v>50</v>
@@ -14152,7 +14080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -14167,7 +14095,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14186,11 +14114,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -14199,7 +14127,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
@@ -14217,7 +14145,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -14232,26 +14160,30 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -14260,7 +14192,7 @@
         <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -14288,23 +14220,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -14312,13 +14244,13 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
+          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
         <v>50</v>
@@ -14354,7 +14286,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
+          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -14373,7 +14305,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-1203a537-115/704225</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -14415,7 +14347,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -14434,7 +14366,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -14471,23 +14403,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Converse Shai 001 Pink</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -14495,7 +14427,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -14513,7 +14445,7 @@
         <v>46093</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -14537,18 +14469,18 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Converse Shai 001 Pink</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -14556,7 +14488,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
+          <t>https://www.kicksonfire.com/converse-shai-001-pink</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -14583,7 +14515,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -14598,39 +14530,35 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>/launch/t/converse-x-anonymous-club-chuck-70-a18452c-001</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -14648,7 +14576,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -14658,12 +14586,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -14682,11 +14610,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -14695,7 +14623,7 @@
         <v>14</v>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
@@ -14723,23 +14651,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -14747,13 +14679,13 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P22" t="n">
         <v>50</v>
@@ -14789,7 +14721,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -14808,7 +14740,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -14835,7 +14767,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14850,26 +14782,26 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>New Balance 1890 Faded Black / Utility Green</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>kicksonfire</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -14878,7 +14810,7 @@
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -14896,7 +14828,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -14911,26 +14843,26 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>New Balance 1890 Faded Black / Utility Green</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>kicksonfire</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.kicksonfire.com/sneaker-release-dates</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://www.kicksonfire.com/new-balance-1890-faded-black-utility-green</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -14939,7 +14871,7 @@
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -14952,7 +14884,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -14967,27 +14899,23 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -14995,13 +14923,13 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
         <v>50</v>
@@ -15022,12 +14950,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -15037,30 +14965,30 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
+          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://www.footlocker.com/release-calendar/nike/K0892600.html</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -15069,7 +14997,7 @@
         <v>22</v>
       </c>
       <c r="P27" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -15082,17 +15010,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -15102,35 +15030,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Kobe 3 Low Protro Pink Quartz</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P28" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -15163,7 +15095,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -15182,7 +15114,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -15224,18 +15156,18 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -15243,7 +15175,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41701706.html</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -17818,7 +17750,7 @@
         <v>46095</v>
       </c>
       <c r="B72" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -19705,7 +19637,7 @@
     </row>
     <row r="102">
       <c r="A102" s="14" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -19727,12 +19659,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+          <t>Nike Air Force 1 Low 'Team USA' From £ 110</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -19751,13 +19683,13 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-team-usa-iq0407-100/706740</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P102" t="n">
         <v>50</v>
@@ -19766,14 +19698,14 @@
     </row>
     <row r="103">
       <c r="A103" s="14" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -19788,15 +19720,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Nike Air Max 95 SE 'England'</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -19812,13 +19748,13 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-se-england-iq0176-100/706661</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P103" t="n">
         <v>50</v>
@@ -19827,14 +19763,14 @@
     </row>
     <row r="104">
       <c r="A104" s="14" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -19854,12 +19790,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+          <t>Nike Air Max Plus 'French Football Federation' From £ 185</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -19877,13 +19813,13 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-plus-french-football-federation-iq0170-400/706739</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P104" t="n">
         <v>50</v>
@@ -19914,12 +19850,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -19938,13 +19874,13 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P105" t="n">
         <v>50</v>
@@ -19960,7 +19896,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -19975,19 +19911,15 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>collab, running, exclusive</t>
-        </is>
-      </c>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -20003,13 +19935,13 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="P106" t="n">
         <v>50</v>
@@ -20018,14 +19950,14 @@
     </row>
     <row r="107">
       <c r="A107" s="14" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B107" t="n">
         <v>0</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -20045,18 +19977,22 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Fragment Design x Nike Air Liquid Max 'Black' From £ 210</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -20064,13 +20000,13 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/fragment-design-x-nike-air-max-liquid-black-iq8601-001/706643</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="P107" t="n">
         <v>50</v>
@@ -20079,7 +20015,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -20106,7 +20042,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Air Liquid Max 'Green Apple' From £ 210</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -20125,7 +20061,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-air-liquid-max-green-apple-iq7634-001/706644</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -20137,6 +20073,132 @@
         <v>50</v>
       </c>
       <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson' From £ 150</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>collab, running, exclusive</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/patta-x-nike-air-max-1-87-ii7055-100/635499</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>40</v>
+      </c>
+      <c r="P109" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>12</v>
+      </c>
+      <c r="P110" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20318,7 +20380,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -20328,7 +20390,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5"/>
@@ -20346,7 +20408,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -20356,7 +20418,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -20386,7 +20448,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -20464,7 +20526,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -20502,7 +20564,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Raw Data" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="High Hype" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="How Scores Work" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +83,24 @@
       <b val="1"/>
       <color rgb="00FFE699"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF8080"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -132,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +205,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1061,7 +1104,7 @@
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr"/>
@@ -1115,7 +1158,7 @@
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr"/>
@@ -1173,7 +1216,7 @@
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr"/>
@@ -1227,7 +1270,7 @@
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr"/>
@@ -1281,7 +1324,7 @@
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="P14" s="12" t="inlineStr"/>
@@ -2587,7 +2630,7 @@
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr"/>
@@ -2645,7 +2688,7 @@
       </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="P38" s="12" t="inlineStr"/>
@@ -2699,7 +2742,7 @@
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr"/>
@@ -2757,7 +2800,7 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr"/>
@@ -2815,7 +2858,7 @@
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr"/>
@@ -3063,17 +3106,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="63" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3115,1764 +3158,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Overkill x adidas Spiritain 2000 'Light Sand'</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SOURCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sourcePrimary</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>thedropdate</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SOURCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sourceSecondary</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://thedropdate.com/releases</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown'</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl'</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Adidas Hyperboost Edge Cloud White / Pure Ruby</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce'</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>adidas Adizero Dropset Elite 'Solar Red'</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG Sail / Off White</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Air Jordan 3 'Spring Is In The Air'</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Balenciaga 3xl Lace WMNS White / Light Pink</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Balenciaga Monday Ultra Brown / White</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Balenciaga Monday Ultra Khaki / White</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Balenciaga Monday Ultra WMNS Lilac / White</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Balenciaga Runner Led Black</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Balenciaga Soleless Black / White</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Balenciaga Triple S Canvas Black</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>C.P. Company x ASICS GEL-QUANTUM 360 I 'Black'</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fragment x Nike Mind 002 'Particle Grey'</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nikes G.t. Cut 4 Pinksicle / Vivid Pink</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Vans LX Old Skool 36 'Pearlised Navy &amp; Black'</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Vans Premium Classic Slip-On 98 'Pearlized Indigo'</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ASICS GEL-CUMULUS 16 'Cream &amp; Beniimo Purple'</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>C.P. Company x ASICS GEL-QUANTUM 360 I 'Moroccan Blue'</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>C.P. Company x ASICS GEL-QUANTUM 360 I 'Pure Silver &amp; Caviar'</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Fragment x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey'</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Nike G.t. Cut 1 Orange Pulse / Persian Violet</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Nike G.t. Future Unseen Hours</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Teyana Taylor x Air Jordan 3 SP 'Concrete Rose'</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 Low White / Blue Tint / Pure Platinum</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Nike Book 2 Must Be The Denim</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Nike First Sight Noir WMNS 'Black'</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Nike First Sight Noir WMNS 'Electric Green'</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Nike First Sight Noir WMNS Black / Metallic Dark Grey</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike First Sight Noir WMNS Electric Green / Racer Blue</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Air Jordan 14 Black / University Blue 2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 Low Team Usa</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 SE 'England'</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Nike Air Max Plus 'French Football Federation'</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low Lower Merion Aces</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low White / Team Red</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Nike Air Max 90 ‘Infrared 3M’</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Fragment Design x Nike Air Liquid Max 'Black'</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>New Balance 1890 'Star Burst'</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Nike Air Liquid Max 'Green Apple'</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Patta x Nike Air Max 1 ’87 'White &amp; Hyper Crimson'</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>PUMA Arizona Lace 'Chocolate Brown'</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>PUMA Arizona Lace WMNS 'Warm White'</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey'</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Slide 'Black'</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black'</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:01:56Z</t>
         </is>
       </c>
     </row>
@@ -5430,7 +3715,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5491,7 +3776,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -5556,7 +3841,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -5617,7 +3902,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5678,7 +3963,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -7149,7 +5434,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -7214,7 +5499,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -7275,7 +5560,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -7340,7 +5625,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -7405,7 +5690,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -8042,4 +6327,345 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>How Scores Work</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>HYPE SCORE  (0–100+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Brand Tier</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>HIGH brands (Air Jordan, Nike, Yeezy, New Balance, Adidas): +12 pts
+MID brands (Vans, Converse, Puma, Reebok, ASICS, Saucony, Hoka, Salomon): +7 pts
+Other brands: +3 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Collab</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Any collab keyword (Travis Scott, Off-White, Supreme, Bad Bunny, Kith…): +20 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Limited / Rare</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Limited, Exclusive, QS, PE, Raffle, Friends &amp; Family, Sample…: +10 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Hot Model</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Jordan 1–13, Dunk, Air Max, Kobe, Yeezy Boost, Samba, NB 550/990…: +12 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Retro / Heritage</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Retro, OG, Original, Vintage, Heritage: +4 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Price Signal</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Retail ≥ $250 OR retail ≤ $110: +3 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Resale Ratio</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Market ÷ Retail ≥ 2.5×: +35 pts  |  ≥ 2.0×: +28  |  ≥ 1.5×: +18  |  ≥ 1.2×: +8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Resale Spread</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Market − Retail ≥ $200: +15 pts  |  ≥ $150: +10  |  ≥ $75: +6  |  ≥ $30: +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Hype Level</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>HIGH ≥ 42 pts     MED ≥ 20 pts     LOW &lt; 20 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>CONFIDENCE SCORE  (0–100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Primary Source</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Release confirmed by primary scraper (GOAT): +25 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Secondary Source</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Confirmed by at least one additional source: +15 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Retail Price</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>retailPrice field is populated: +15 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>imageUrl field is populated: +10 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Release URL</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>releaseUrl field is populated: +10 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Source Count</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Seen by 3+ sources: +28 pts  |  Seen by 2 sources: +18 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Single-source cap</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Releases seen by only 1 source are capped at 59 (cannot reach HIGH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Confidence Level</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>HIGH ≥ 60 pts     MED ≥ 32 pts     LOW &lt; 32 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Must Watch</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Hype = HIGH  AND  Confidence = HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Hype = HIGH + Confidence = MED, OR Hype = MED + Confidence = HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>All other hype / confidence combinations</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>FLIP SCORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Flip % = round((Market Value − Retail Price) / Retail Price × 100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>$150 retail, $225 market  →  Flip % = +50%  (50% above retail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>No value</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Shown as blank when retail or market value is missing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -715,9 +715,7 @@
       <c r="A4" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
@@ -734,7 +732,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -771,9 +769,7 @@
       <c r="A5" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
@@ -790,7 +786,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -827,9 +823,7 @@
       <c r="A6" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr">
@@ -846,7 +840,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -887,9 +881,7 @@
       <c r="A7" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="13" t="inlineStr">
@@ -906,7 +898,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -947,9 +939,7 @@
       <c r="A8" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
@@ -966,7 +956,7 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1067,9 +1057,7 @@
       <c r="A10" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr">
@@ -1086,7 +1074,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1405,9 +1393,7 @@
       <c r="A16" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr">
@@ -1424,7 +1410,7 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1465,9 +1451,7 @@
       <c r="A17" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
@@ -1484,7 +1468,7 @@
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
@@ -1521,9 +1505,7 @@
       <c r="A18" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
@@ -1540,7 +1522,7 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -1581,9 +1563,7 @@
       <c r="A19" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr">
@@ -1600,7 +1580,7 @@
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
@@ -1637,9 +1617,7 @@
       <c r="A20" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="13" t="inlineStr">
@@ -1656,7 +1634,7 @@
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
@@ -1697,9 +1675,7 @@
       <c r="A21" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
@@ -1716,7 +1692,7 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
@@ -1757,9 +1733,7 @@
       <c r="A22" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
@@ -1776,7 +1750,7 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
@@ -1817,9 +1791,7 @@
       <c r="A23" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B23" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
@@ -1836,7 +1808,7 @@
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
@@ -1873,9 +1845,7 @@
       <c r="A24" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
@@ -1892,7 +1862,7 @@
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -1929,9 +1899,7 @@
       <c r="A25" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B25" s="5" t="inlineStr"/>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
@@ -1948,7 +1916,7 @@
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
@@ -1985,9 +1953,7 @@
       <c r="A26" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr">
@@ -2004,7 +1970,7 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2045,9 +2011,7 @@
       <c r="A27" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
@@ -2064,7 +2028,7 @@
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
@@ -2105,9 +2069,7 @@
       <c r="A28" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr">
@@ -2124,7 +2086,7 @@
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -2165,9 +2127,7 @@
       <c r="A29" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr">
@@ -2184,7 +2144,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2225,9 +2185,7 @@
       <c r="A30" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="13" t="inlineStr">
@@ -2244,7 +2202,7 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2285,9 +2243,7 @@
       <c r="A31" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="13" t="inlineStr">
@@ -2304,7 +2260,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2345,9 +2301,7 @@
       <c r="A32" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
@@ -2364,7 +2318,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2405,9 +2359,7 @@
       <c r="A33" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
@@ -2424,7 +2376,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2465,9 +2417,7 @@
       <c r="A34" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
@@ -2484,7 +2434,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2521,9 +2471,7 @@
       <c r="A35" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B35" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
@@ -2540,7 +2488,7 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
@@ -2635,9 +2583,7 @@
       <c r="A37" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="7" t="inlineStr">
@@ -2654,7 +2600,7 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
@@ -2981,9 +2927,7 @@
       <c r="A43" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>130</v>
-      </c>
+      <c r="B43" s="5" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
@@ -3000,7 +2944,7 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
@@ -3041,9 +2985,7 @@
       <c r="A44" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>130</v>
-      </c>
+      <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
@@ -3060,7 +3002,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3097,9 +3039,7 @@
       <c r="A45" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>130</v>
-      </c>
+      <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
@@ -3116,7 +3056,7 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
@@ -3157,9 +3097,7 @@
       <c r="A46" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B46" s="5" t="n">
-        <v>130</v>
-      </c>
+      <c r="B46" s="5" t="inlineStr"/>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
       <c r="E46" s="7" t="inlineStr">
@@ -3176,7 +3114,7 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
@@ -3228,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3286,7 +3224,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3296,20 +3234,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3281,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3341,17 +3291,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3318,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3383,17 +3333,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3360,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3425,17 +3375,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3407,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3467,17 +3417,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3444,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3509,17 +3459,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3486,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3551,17 +3501,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3533,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3593,17 +3543,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3570,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3635,17 +3585,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3617,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3677,17 +3627,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3659,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3719,17 +3669,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3701,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3761,17 +3711,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3743,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3803,17 +3753,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3785,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3845,17 +3795,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3827,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3887,17 +3837,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3869,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3929,17 +3879,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3911,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3971,17 +3921,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4003,7 +3953,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4013,17 +3963,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4045,7 +3995,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4055,17 +4005,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4037,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4097,17 +4047,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4079,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4139,17 +4089,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4121,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4181,17 +4131,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4158,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4223,17 +4173,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4205,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4265,17 +4215,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4247,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4307,17 +4257,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4284,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4349,17 +4299,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4331,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4391,17 +4341,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4413,17 +4363,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4433,17 +4383,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4460,12 +4410,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4475,17 +4425,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4502,12 +4452,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4517,17 +4467,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4499,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4559,59 +4509,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-14T05:32:01Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:32:01Z</t>
+          <t>2026-03-14T05:36:08Z</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4648,7 @@
         <v>46095</v>
       </c>
       <c r="B2" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4792,7 +4700,7 @@
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
@@ -4801,7 +4709,7 @@
         <v>46095</v>
       </c>
       <c r="B3" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4853,7 +4761,7 @@
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -4862,7 +4770,7 @@
         <v>46095</v>
       </c>
       <c r="B4" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4918,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -4927,7 +4835,7 @@
         <v>46095</v>
       </c>
       <c r="B5" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4983,7 +4891,7 @@
         <v>38</v>
       </c>
       <c r="P5" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -4992,7 +4900,7 @@
         <v>46095</v>
       </c>
       <c r="B6" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5048,7 +4956,7 @@
         <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -5122,7 +5030,7 @@
         <v>46095</v>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5178,7 +5086,7 @@
         <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -5500,7 +5408,7 @@
         <v>46095</v>
       </c>
       <c r="B14" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5556,7 +5464,7 @@
         <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -5565,7 +5473,7 @@
         <v>46095</v>
       </c>
       <c r="B15" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5617,7 +5525,7 @@
         <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -5626,7 +5534,7 @@
         <v>46095</v>
       </c>
       <c r="B16" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5682,7 +5590,7 @@
         <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -5691,7 +5599,7 @@
         <v>46095</v>
       </c>
       <c r="B17" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5743,7 +5651,7 @@
         <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -5752,7 +5660,7 @@
         <v>46095</v>
       </c>
       <c r="B18" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -5808,7 +5716,7 @@
         <v>24</v>
       </c>
       <c r="P18" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -5817,7 +5725,7 @@
         <v>46095</v>
       </c>
       <c r="B19" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -5873,7 +5781,7 @@
         <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
@@ -5882,7 +5790,7 @@
         <v>46095</v>
       </c>
       <c r="B20" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -5938,7 +5846,7 @@
         <v>22</v>
       </c>
       <c r="P20" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -5947,7 +5855,7 @@
         <v>46095</v>
       </c>
       <c r="B21" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -5999,7 +5907,7 @@
         <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
@@ -6008,7 +5916,7 @@
         <v>46095</v>
       </c>
       <c r="B22" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6060,7 +5968,7 @@
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -6069,7 +5977,7 @@
         <v>46095</v>
       </c>
       <c r="B23" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6121,7 +6029,7 @@
         <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -6130,7 +6038,7 @@
         <v>46095</v>
       </c>
       <c r="B24" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6186,7 +6094,7 @@
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -6195,7 +6103,7 @@
         <v>46095</v>
       </c>
       <c r="B25" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6251,7 +6159,7 @@
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -6260,7 +6168,7 @@
         <v>46095</v>
       </c>
       <c r="B26" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6316,7 +6224,7 @@
         <v>24</v>
       </c>
       <c r="P26" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -6325,7 +6233,7 @@
         <v>46095</v>
       </c>
       <c r="B27" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6381,7 +6289,7 @@
         <v>24</v>
       </c>
       <c r="P27" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -6390,7 +6298,7 @@
         <v>46095</v>
       </c>
       <c r="B28" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6446,7 +6354,7 @@
         <v>24</v>
       </c>
       <c r="P28" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -6455,7 +6363,7 @@
         <v>46095</v>
       </c>
       <c r="B29" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6511,7 +6419,7 @@
         <v>24</v>
       </c>
       <c r="P29" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -6520,7 +6428,7 @@
         <v>46095</v>
       </c>
       <c r="B30" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6576,7 +6484,7 @@
         <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -6585,7 +6493,7 @@
         <v>46095</v>
       </c>
       <c r="B31" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6641,7 +6549,7 @@
         <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -6650,7 +6558,7 @@
         <v>46095</v>
       </c>
       <c r="B32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6702,7 +6610,7 @@
         <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -6711,7 +6619,7 @@
         <v>46095</v>
       </c>
       <c r="B33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6767,7 +6675,7 @@
         <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -6841,7 +6749,7 @@
         <v>46095</v>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6897,7 +6805,7 @@
         <v>17</v>
       </c>
       <c r="P35" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -7227,7 +7135,7 @@
         <v>46113</v>
       </c>
       <c r="B41" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7283,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="P41" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
@@ -7292,7 +7200,7 @@
         <v>46113</v>
       </c>
       <c r="B42" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7344,7 +7252,7 @@
         <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -7353,7 +7261,7 @@
         <v>46113</v>
       </c>
       <c r="B43" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7409,7 +7317,7 @@
         <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
@@ -7418,7 +7326,7 @@
         <v>46113</v>
       </c>
       <c r="B44" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -7474,7 +7382,7 @@
         <v>7</v>
       </c>
       <c r="P44" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -609,10 +609,11 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="11" max="11"/>
     <col width="33" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="70" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -692,20 +693,25 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>Source Primary</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Source Count</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Release URL</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -752,20 +758,21 @@
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="O4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/adidas/JQ9497.html</t>
         </is>
       </c>
-      <c r="P4" s="12" t="inlineStr"/>
+      <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -808,20 +815,21 @@
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="O5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
-      <c r="P5" s="12" t="inlineStr"/>
+      <c r="Q5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -870,18 +878,23 @@
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="O6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
         </is>
       </c>
-      <c r="P6" s="12" t="inlineStr"/>
+      <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -930,18 +943,23 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="O7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
-      <c r="P7" s="12" t="inlineStr"/>
+      <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -988,20 +1006,21 @@
           <t>retro, kids</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="O8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
-      <c r="P8" s="12" t="inlineStr"/>
+      <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1048,20 +1067,21 @@
           <t>retro, kids</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
-      <c r="P9" s="12" t="inlineStr"/>
+      <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1108,20 +1128,21 @@
           <t>retro, kids</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
-      <c r="P10" s="12" t="inlineStr"/>
+      <c r="Q10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1166,20 +1187,21 @@
           <t>hot-model</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="O11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
-      <c r="P11" s="12" t="inlineStr"/>
+      <c r="Q11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1220,20 +1242,21 @@
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="O12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="P12" s="12" t="inlineStr"/>
+      <c r="Q12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1278,20 +1301,21 @@
           <t>hot-model, retro, kids</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="O13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
-      <c r="P13" s="12" t="inlineStr"/>
+      <c r="Q13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1332,20 +1356,21 @@
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="O14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="P14" s="12" t="inlineStr"/>
+      <c r="Q14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1386,20 +1411,21 @@
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="12" t="inlineStr">
+      <c r="O15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="P15" s="12" t="inlineStr"/>
+      <c r="Q15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1446,20 +1472,21 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="12" t="inlineStr">
+      <c r="O16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
-      <c r="P16" s="12" t="inlineStr"/>
+      <c r="Q16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1502,20 +1529,21 @@
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="12" t="inlineStr">
+      <c r="O17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
-      <c r="P17" s="12" t="inlineStr"/>
+      <c r="Q17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1564,18 +1592,23 @@
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="O18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr"/>
+      <c r="Q18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1618,20 +1651,21 @@
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="O19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
-      <c r="P19" s="12" t="inlineStr"/>
+      <c r="Q19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1678,20 +1712,21 @@
           <t>hot-model, running, women</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="12" t="inlineStr">
+      <c r="O20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
-      <c r="P20" s="12" t="inlineStr"/>
+      <c r="Q20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1738,20 +1773,21 @@
           <t>running</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="O21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
-      <c r="P21" s="12" t="inlineStr"/>
+      <c r="Q21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1798,20 +1834,21 @@
           <t>running, exclusive</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="O22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr"/>
+      <c r="Q22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1854,20 +1891,21 @@
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="12" t="inlineStr">
+      <c r="O23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr"/>
+      <c r="Q23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1910,20 +1948,21 @@
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr"/>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="12" t="inlineStr">
+      <c r="O24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
-      <c r="P24" s="12" t="inlineStr"/>
+      <c r="Q24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1966,20 +2005,21 @@
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="12" t="inlineStr">
+      <c r="O25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
-      <c r="P25" s="12" t="inlineStr"/>
+      <c r="Q25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2026,20 +2066,21 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr">
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="O26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
-      <c r="P26" s="12" t="inlineStr"/>
+      <c r="Q26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2086,20 +2127,21 @@
           <t>basketball</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" s="12" t="inlineStr">
+      <c r="O27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
-      <c r="P27" s="12" t="inlineStr"/>
+      <c r="Q27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2146,20 +2188,21 @@
           <t>hot-model, basketball</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" s="12" t="inlineStr">
+      <c r="O28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
-      <c r="P28" s="12" t="inlineStr"/>
+      <c r="Q28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2206,20 +2249,21 @@
           <t>hot-model, basketball</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="12" t="inlineStr">
+      <c r="O29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
-      <c r="P29" s="12" t="inlineStr"/>
+      <c r="Q29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2266,20 +2310,21 @@
           <t>hot-model, basketball</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="12" t="inlineStr">
+      <c r="O30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
-      <c r="P30" s="12" t="inlineStr"/>
+      <c r="Q30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2326,20 +2371,21 @@
           <t>hot-model, basketball, kids</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="12" t="inlineStr">
+      <c r="O31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
-      <c r="P31" s="12" t="inlineStr"/>
+      <c r="Q31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2386,20 +2432,21 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="12" t="inlineStr">
+      <c r="O32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
-      <c r="P32" s="12" t="inlineStr"/>
+      <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2446,20 +2493,21 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr"/>
+      <c r="N33" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="12" t="inlineStr">
+      <c r="O33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
-      <c r="P33" s="12" t="inlineStr"/>
+      <c r="Q33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2502,20 +2550,21 @@
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr"/>
-      <c r="M34" s="6" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr"/>
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" s="12" t="inlineStr">
+      <c r="O34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
-      <c r="P34" s="12" t="inlineStr"/>
+      <c r="Q34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2562,20 +2611,21 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" s="12" t="inlineStr">
+      <c r="O35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
-      <c r="P35" s="12" t="inlineStr"/>
+      <c r="Q35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2618,20 +2668,21 @@
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr"/>
-      <c r="M36" s="6" t="inlineStr">
+      <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" s="12" t="inlineStr">
+      <c r="O36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="12" t="inlineStr">
         <is>
           <t>#main</t>
         </is>
       </c>
-      <c r="P36" s="12" t="inlineStr"/>
+      <c r="Q36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2680,18 +2731,23 @@
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" s="12" t="inlineStr">
+      <c r="O37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
-      <c r="P37" s="12" t="inlineStr"/>
+      <c r="Q37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2736,20 +2792,21 @@
           <t>hot-model, retro</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr">
+      <c r="M38" s="6" t="inlineStr"/>
+      <c r="N38" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" s="12" t="inlineStr">
+      <c r="O38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
-      <c r="P38" s="12" t="inlineStr"/>
+      <c r="Q38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2794,20 +2851,21 @@
           <t>hot-model, retro</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="O39" s="12" t="inlineStr">
+      <c r="P39" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
-      <c r="P39" s="12" t="inlineStr"/>
+      <c r="Q39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2848,20 +2906,21 @@
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
-      <c r="M40" s="6" t="inlineStr">
+      <c r="M40" s="6" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" s="12" t="inlineStr">
+      <c r="O40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="P40" s="12" t="inlineStr"/>
+      <c r="Q40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2906,20 +2965,21 @@
           <t>hot-model, running</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" s="12" t="inlineStr">
+      <c r="O41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
-      <c r="P41" s="12" t="inlineStr"/>
+      <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2964,37 +3024,36 @@
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="M42" s="6" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" s="12" t="inlineStr">
+      <c r="O42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
-      <c r="P42" s="12" t="inlineStr"/>
+      <c r="Q42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46099</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>16</v>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3002,7 +3061,7 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
@@ -3016,45 +3075,44 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="P43" s="12" t="inlineStr"/>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="Q43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46102</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>12</v>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3062,7 +3120,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3071,29 +3129,34 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="N44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="P44" s="12" t="inlineStr"/>
+          <t>Mar 21 Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="Q44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -3110,7 +3173,7 @@
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3127,33 +3190,34 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="P45" s="12" t="inlineStr"/>
+      <c r="O45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -3170,7 +3234,7 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3187,38 +3251,157 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
           <t>Vans</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr">
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
-      <c r="L46" s="12" t="inlineStr">
+      <c r="L48" s="12" t="inlineStr">
         <is>
           <t>women</t>
         </is>
       </c>
-      <c r="M46" s="6" t="inlineStr">
+      <c r="M48" s="6" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" s="12" t="inlineStr">
+      <c r="O48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="P46" s="12" t="inlineStr"/>
+      <c r="Q48" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3230,17 +3413,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3282,6 +3465,66 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:23:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mar 21 Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:23:02Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3307,15 +3550,16 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="70" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="70" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3361,45 +3605,50 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Source Primary</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Source Secondary</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Source Count</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Release URL</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Hype Score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Confidence Score</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Market Value</t>
         </is>
@@ -3438,33 +3687,34 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/adidas/JQ9497.html</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>12</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>59</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="n">
@@ -3499,33 +3749,34 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>59</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="18" t="n">
@@ -3566,31 +3817,36 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>16</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>59</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="n">
@@ -3631,31 +3887,36 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>38</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>59</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n">
@@ -3694,33 +3955,34 @@
           <t>retro, kids</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>16</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>59</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="n">
@@ -3759,33 +4021,34 @@
           <t>retro, kids</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>16</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>83</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="n">
@@ -3824,33 +4087,34 @@
           <t>retro, kids</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>16</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>59</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n">
@@ -3889,33 +4153,34 @@
           <t>hot-model</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>24</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>50</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n">
@@ -3950,33 +4215,34 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>12</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>50</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="n">
@@ -4015,33 +4281,34 @@
           <t>hot-model, retro, kids</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>28</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>50</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n">
@@ -4076,33 +4343,34 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>12</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>50</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n">
@@ -4137,33 +4405,34 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>12</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>50</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n">
@@ -4202,33 +4471,34 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>7</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>59</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n">
@@ -4263,33 +4533,34 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>7</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>59</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n">
@@ -4330,31 +4601,36 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>7</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>59</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
@@ -4389,33 +4665,34 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>12</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>59</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
@@ -4454,33 +4731,34 @@
           <t>hot-model, running, women</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>24</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>59</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
@@ -4519,33 +4797,34 @@
           <t>running</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>12</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>59</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
@@ -4584,33 +4863,34 @@
           <t>running, exclusive</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>22</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>59</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
@@ -4645,33 +4925,34 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>12</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>59</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="18" t="n">
@@ -4706,33 +4987,34 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>12</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>59</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
@@ -4767,33 +5049,34 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>12</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>59</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
@@ -4832,33 +5115,34 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>12</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>59</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="18" t="n">
@@ -4897,33 +5181,34 @@
           <t>basketball</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>12</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>59</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="18" t="n">
@@ -4962,33 +5247,34 @@
           <t>hot-model, basketball</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>24</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>59</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="18" t="n">
@@ -5027,33 +5313,34 @@
           <t>hot-model, basketball</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>24</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>59</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
@@ -5092,33 +5379,34 @@
           <t>hot-model, basketball</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>24</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>59</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
@@ -5157,33 +5445,34 @@
           <t>hot-model, basketball, kids</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>24</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>59</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
@@ -5222,33 +5511,34 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>12</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>59</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
@@ -5287,33 +5577,34 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
         <v>7</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>59</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
@@ -5348,33 +5639,34 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>7</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>59</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
@@ -5413,33 +5705,34 @@
           <t>kids</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>7</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>59</v>
       </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
@@ -5474,37 +5767,38 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>#main</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://images.footlocker.com/content/dam/final/footlocker/site/homepage/2026/february/260225-fl-flca-recrne5wvpiszp57g-top-nav-image-update/260225-fl-flca-recRNe5WvpISZp57G-top-nav-image-update-mens-basketball.jpg</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>59</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
@@ -5545,31 +5839,36 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>17</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>59</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
@@ -5608,33 +5907,34 @@
           <t>hot-model, retro</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>28</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>50</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="18" t="n">
@@ -5673,33 +5973,34 @@
           <t>hot-model, retro</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>2</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>28</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>68</v>
       </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="18" t="n">
@@ -5734,33 +6035,34 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch</t>
         </is>
       </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
         <v>12</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>50</v>
       </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="n">
@@ -5799,33 +6101,34 @@
           <t>hot-model, running</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
         <v>24</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>50</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="18" t="n">
@@ -5864,44 +6167,45 @@
           <t>lifestyle</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
         <v>7</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>50</v>
       </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="18" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B41" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5921,52 +6225,53 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>16</v>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>50</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="18" t="n">
-        <v>46113</v>
+        <v>46102</v>
       </c>
       <c r="B42" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5981,42 +6286,47 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
+          <t>Mar 21 Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
-        <v>12</v>
-      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>50</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="18" t="n">
@@ -6042,46 +6352,47 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
-        <v>7</v>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q43" t="n">
         <v>59</v>
       </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n">
@@ -6107,46 +6418,175 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>59</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B45" t="n">
+        <v>130</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Vans</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>59</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B46" t="n">
+        <v>130</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>women</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="inlineStr">
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
         <v>7</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q46" t="n">
         <v>59</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6159,7 +6599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6174,10 +6614,11 @@
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6257,20 +6698,25 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>Source Primary</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Source Count</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Release URL</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6295,13 +6741,14 @@
       <c r="L4" s="12" t="n"/>
       <c r="M4" s="6" t="n"/>
       <c r="N4" s="6" t="n"/>
-      <c r="O4" s="12" t="n"/>
+      <c r="O4" s="6" t="n"/>
       <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6335,7 +6782,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4"/>
@@ -6350,7 +6797,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6360,11 +6807,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -6462,7 +6909,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -6500,7 +6947,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,17 +71,6 @@
     </font>
     <font>
       <color rgb="00FFC000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007CFCFF"/>
-    </font>
-    <font>
-      <color rgb="007CFCFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFE699"/>
     </font>
     <font>
       <b val="1"/>
@@ -137,6 +126,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="007CFCFF"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFC000"/>
       <sz val="12"/>
     </font>
@@ -170,6 +163,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FF8080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFE699"/>
     </font>
   </fonts>
   <fills count="6">
@@ -226,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -270,32 +267,32 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -311,52 +308,43 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -365,16 +353,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -742,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -756,7 +744,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="11" max="11"/>
-    <col width="33" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -867,7 +855,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
@@ -895,12 +883,12 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>adidas DON Issue 7 "Best Of Adi"</t>
+          <t>Jacquemus x Nike Moon Shoe</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr"/>
@@ -915,14 +903,14 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/26/adidas-don-issue-7-black-gold-jq9435</t>
+          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
@@ -933,7 +921,7 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -955,18 +943,18 @@
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -974,52 +962,52 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
@@ -1029,20 +1017,22 @@
         </is>
       </c>
       <c r="O6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr">
@@ -1059,7 +1049,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -1068,19 +1058,19 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1088,14 +1078,14 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46096</v>
+        <v>46099</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
@@ -1106,7 +1096,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1123,17 +1113,17 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr"/>
@@ -1147,25 +1137,27 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>12</v>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>38</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1173,7 +1165,7 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1182,19 +1174,27 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1202,16 +1202,18 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="13" t="inlineStr">
@@ -1220,7 +1222,7 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1228,7 +1230,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1242,18 +1244,22 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1261,16 +1267,18 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
@@ -1279,7 +1287,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1287,7 +1295,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1296,23 +1304,23 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1320,7 +1328,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -1340,7 +1348,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1357,15 +1365,19 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -1377,7 +1389,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1386,16 +1398,18 @@
       <c r="A13" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>28</v>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1403,7 +1417,7 @@
         </is>
       </c>
       <c r="H13" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
@@ -1412,23 +1426,23 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O13" s="6" t="n">
@@ -1436,7 +1450,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1450,13 +1464,13 @@
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>38</v>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1473,24 +1487,16 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1501,7 +1507,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1521,7 +1527,7 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1538,17 +1544,17 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
+          <t>basketball, exclusive</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -1566,7 +1572,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -1586,7 +1592,7 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1603,19 +1609,15 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr">
         <is>
@@ -1627,7 +1629,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1641,13 +1643,13 @@
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>16</v>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1664,17 +1666,17 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
@@ -1688,7 +1690,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1708,7 +1710,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1725,17 +1727,17 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr"/>
@@ -1749,7 +1751,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1763,13 +1765,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>7</v>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>22</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1786,15 +1788,19 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1806,7 +1812,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1820,13 +1826,13 @@
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>22</v>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1848,19 +1854,11 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1871,7 +1869,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1913,7 +1911,7 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr"/>
@@ -1928,7 +1926,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1942,13 +1940,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>24</v>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1970,14 +1968,10 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr"/>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -1989,7 +1983,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2031,12 +2025,12 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
@@ -2050,7 +2044,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2070,7 +2064,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2092,12 +2086,12 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr"/>
@@ -2111,7 +2105,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2125,13 +2119,13 @@
       </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>12</v>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2153,10 +2147,14 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="inlineStr"/>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -2168,7 +2166,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2182,13 +2180,13 @@
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>12</v>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2210,10 +2208,14 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr"/>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M26" s="6" t="inlineStr"/>
       <c r="N26" s="6" t="inlineStr">
         <is>
@@ -2225,7 +2227,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2239,13 +2241,13 @@
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>12</v>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2267,10 +2269,14 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
       <c r="M27" s="6" t="inlineStr"/>
       <c r="N27" s="6" t="inlineStr">
         <is>
@@ -2282,7 +2288,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2324,7 +2330,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
@@ -2343,7 +2349,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2352,18 +2358,16 @@
       <c r="A29" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>210</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>24</v>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2371,7 +2375,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2385,18 +2389,18 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2404,7 +2408,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2418,13 +2422,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>24</v>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2441,17 +2445,17 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2465,7 +2469,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2479,13 +2483,13 @@
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>24</v>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2502,19 +2506,15 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2540,13 +2540,13 @@
       </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>24</v>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2563,17 +2563,17 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2624,19 +2624,15 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
@@ -2648,7 +2644,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -2657,7 +2653,9 @@
       <c r="A34" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
@@ -2666,7 +2664,7 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2683,23 +2681,19 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O34" s="6" t="n">
@@ -2707,7 +2701,7 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
@@ -2727,7 +2721,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2744,19 +2738,15 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr">
         <is>
@@ -2768,7 +2758,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -2788,7 +2778,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2805,12 +2795,12 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr"/>
@@ -2825,7 +2815,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -2845,7 +2835,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2862,19 +2852,15 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
@@ -2886,7 +2872,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -2928,7 +2914,7 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr"/>
@@ -2943,7 +2929,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -2985,7 +2971,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr"/>
@@ -3000,7 +2986,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -3042,7 +3028,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
@@ -3057,7 +3043,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -3077,7 +3063,7 @@
         </is>
       </c>
       <c r="F41" s="8" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -3094,16 +3080,24 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr"/>
-      <c r="M41" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3114,27 +3108,25 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>3</v>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>32</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -3142,7 +3134,7 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -3151,19 +3143,23 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr"/>
+          <t>Fragment Design x Nike Book 2</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="M42" s="6" t="inlineStr"/>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O42" s="6" t="n">
@@ -3171,27 +3167,25 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>3</v>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>32</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3199,7 +3193,7 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
@@ -3208,19 +3202,23 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr"/>
+          <t>Fragment Design x Nike Mind 001</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="inlineStr"/>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O43" s="6" t="n">
@@ -3228,27 +3226,25 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>3</v>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>34</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3256,7 +3252,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3265,19 +3261,23 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr"/>
+          <t>Nike Air Max 90 QS</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
       <c r="M44" s="6" t="inlineStr"/>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O44" s="6" t="n">
@@ -3285,18 +3285,16 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
@@ -3305,7 +3303,7 @@
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3322,19 +3320,19 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Nike GT Future</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr"/>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3342,18 +3340,16 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr"/>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
       <c r="E46" s="7" t="inlineStr">
@@ -3362,7 +3358,7 @@
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3379,27 +3375,19 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3407,14 +3395,14 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="5" t="inlineStr"/>
@@ -3425,7 +3413,7 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3433,7 +3421,7 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
@@ -3442,23 +3430,23 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -3466,14 +3454,14 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr"/>
@@ -3484,7 +3472,7 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3492,7 +3480,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3506,18 +3494,18 @@
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -3525,25 +3513,27 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>28</v>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3551,7 +3541,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
@@ -3565,18 +3555,18 @@
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -3584,25 +3574,27 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B50" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>24</v>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3610,7 +3602,7 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3624,18 +3616,14 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -3643,7 +3631,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
@@ -3663,7 +3651,7 @@
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3680,17 +3668,17 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
@@ -3704,7 +3692,7 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
@@ -3724,7 +3712,7 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3741,15 +3729,19 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr"/>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M52" s="6" t="inlineStr"/>
       <c r="N52" s="6" t="inlineStr">
         <is>
@@ -3761,132 +3753,10 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="6" t="inlineStr"/>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P53" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="Q53" s="12" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="6" t="inlineStr"/>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="Q54" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3903,13 +3773,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -3961,22 +3831,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>adidas DON Issue 7 "Best Of Adi"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3984,19 +3854,19 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-15T17:02:39Z</t>
+          <t>2026-03-16T08:00:07Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4006,7 +3876,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -4014,29 +3884,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-15T17:02:39Z</t>
+          <t>2026-03-16T08:00:07Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Air Jordan 14 Retro Black and University Blue</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -4044,7 +3914,157 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-15T17:02:39Z</t>
+          <t>2026-03-16T08:00:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-16T08:00:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-16T08:00:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nike Air Max 90 QS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-16T08:00:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-16T08:00:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-16T08:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4069,7 +4089,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="54" customWidth="1" min="11" max="11"/>
@@ -4175,8 +4195,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
-        <v>46096</v>
+      <c r="A2" s="15" t="n">
+        <v>46097</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -4198,12 +4218,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>adidas DON Issue 7 "Best Of Adi"</t>
+          <t>Jacquemus x Nike Moon Shoe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -4223,7 +4243,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/26/adidas-don-issue-7-black-gold-jq9435</t>
+          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -4237,8 +4257,8 @@
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
-        <v>46096</v>
+      <c r="A3" s="15" t="n">
+        <v>46098</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -4265,23 +4285,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -4289,13 +4309,13 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
@@ -4303,40 +4323,40 @@
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
-        <v>46096</v>
+      <c r="A4" s="15" t="n">
+        <v>46098</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4347,33 +4367,33 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>46096</v>
+      <c r="A5" s="15" t="n">
+        <v>46099</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4392,24 +4412,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -4417,7 +4437,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -4426,13 +4446,13 @@
         <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>46096</v>
+      <c r="A6" s="15" t="n">
+        <v>46099</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -4454,17 +4474,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -4475,7 +4495,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -4483,13 +4503,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -4497,15 +4517,15 @@
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>46097</v>
+      <c r="A7" s="15" t="n">
+        <v>46099</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4520,24 +4540,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4545,25 +4573,25 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>46098</v>
+      <c r="A8" s="15" t="n">
+        <v>46099</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -4587,23 +4615,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4611,25 +4643,25 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>46098</v>
+      <c r="A9" s="15" t="n">
+        <v>46099</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4648,28 +4680,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4677,21 +4709,21 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B10" t="n">
@@ -4714,15 +4746,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -4739,13 +4775,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -4753,15 +4789,15 @@
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4776,28 +4812,28 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -4805,21 +4841,21 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B12" t="n">
@@ -4827,7 +4863,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4842,24 +4878,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4875,13 +4903,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -4889,7 +4917,7 @@
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B13" t="n">
@@ -4912,17 +4940,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
+          <t>basketball, exclusive</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4945,13 +4973,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -4959,7 +4987,7 @@
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B14" t="n">
@@ -4982,19 +5010,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
@@ -5011,13 +5035,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -5025,7 +5049,7 @@
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B15" t="n">
@@ -5033,7 +5057,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5048,17 +5072,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -5077,13 +5101,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -5091,7 +5115,7 @@
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B16" t="n">
@@ -5114,17 +5138,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -5143,13 +5167,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -5157,7 +5181,7 @@
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B17" t="n">
@@ -5165,7 +5189,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5180,15 +5204,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
@@ -5205,13 +5233,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -5219,7 +5247,7 @@
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B18" t="n">
@@ -5227,7 +5255,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5247,19 +5275,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5275,13 +5295,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -5289,7 +5309,7 @@
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B19" t="n">
@@ -5317,7 +5337,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -5337,7 +5357,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -5351,7 +5371,7 @@
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B20" t="n">
@@ -5359,7 +5379,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5379,14 +5399,10 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -5403,13 +5419,13 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
         <v>59</v>
@@ -5417,7 +5433,7 @@
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B21" t="n">
@@ -5445,12 +5461,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -5469,7 +5485,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -5483,7 +5499,7 @@
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B22" t="n">
@@ -5511,12 +5527,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -5535,13 +5551,13 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
         <v>59</v>
@@ -5549,7 +5565,7 @@
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B23" t="n">
@@ -5557,7 +5573,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5577,10 +5593,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -5597,13 +5617,13 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -5611,7 +5631,7 @@
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B24" t="n">
@@ -5619,7 +5639,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5639,10 +5659,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
@@ -5659,13 +5683,13 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
         <v>59</v>
@@ -5673,7 +5697,7 @@
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B25" t="n">
@@ -5681,7 +5705,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5701,10 +5725,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
@@ -5721,13 +5749,13 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q25" t="n">
         <v>59</v>
@@ -5735,7 +5763,7 @@
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B26" t="n">
@@ -5763,7 +5791,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -5787,7 +5815,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -5801,15 +5829,15 @@
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B27" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5829,23 +5857,23 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5853,21 +5881,21 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q27" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B28" t="n">
@@ -5875,7 +5903,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5890,17 +5918,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -5919,13 +5947,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -5933,7 +5961,7 @@
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B29" t="n">
@@ -5941,7 +5969,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5956,19 +5984,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -5985,13 +6009,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -5999,7 +6023,7 @@
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B30" t="n">
@@ -6007,7 +6031,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6022,17 +6046,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -6051,13 +6075,13 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
         <v>59</v>
@@ -6065,7 +6089,7 @@
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B31" t="n">
@@ -6088,19 +6112,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
@@ -6117,13 +6137,13 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>59</v>
@@ -6131,11 +6151,11 @@
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6154,28 +6174,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -6183,17 +6199,13 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/4a1c66575467445342b9085cc4510900_1772681368.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>59</v>
@@ -6201,7 +6213,7 @@
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B33" t="n">
@@ -6224,19 +6236,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
@@ -6253,13 +6261,13 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>59</v>
@@ -6267,7 +6275,7 @@
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B34" t="n">
@@ -6290,12 +6298,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -6315,13 +6323,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
         <v>59</v>
@@ -6329,7 +6337,7 @@
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B35" t="n">
@@ -6352,19 +6360,15 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
@@ -6381,13 +6385,13 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
         <v>59</v>
@@ -6395,7 +6399,7 @@
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B36" t="n">
@@ -6423,7 +6427,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6443,7 +6447,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -6457,7 +6461,7 @@
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B37" t="n">
@@ -6485,7 +6489,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6505,7 +6509,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -6519,7 +6523,7 @@
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B38" t="n">
@@ -6547,7 +6551,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6567,7 +6571,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -6581,7 +6585,7 @@
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="15" t="n">
         <v>46099</v>
       </c>
       <c r="B39" t="n">
@@ -6604,16 +6608,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6629,13 +6641,13 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Q39" t="n">
         <v>59</v>
@@ -6643,15 +6655,15 @@
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
-        <v>46099</v>
+      <c r="A40" s="15" t="n">
+        <v>46100</v>
       </c>
       <c r="B40" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6666,24 +6678,28 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Fragment Design x Nike Book 2</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6691,29 +6707,29 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="Q40" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
-        <v>46099</v>
+      <c r="A41" s="15" t="n">
+        <v>46100</v>
       </c>
       <c r="B41" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6728,24 +6744,28 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Fragment Design x Nike Mind 001</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -6753,29 +6773,29 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="Q41" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
-        <v>46099</v>
+      <c r="A42" s="15" t="n">
+        <v>46100</v>
       </c>
       <c r="B42" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6790,24 +6810,28 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Nike Air Max 90 QS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6815,25 +6839,25 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="Q42" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
-        <v>46099</v>
+      <c r="A43" s="15" t="n">
+        <v>46100</v>
       </c>
       <c r="B43" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6852,24 +6876,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Nike GT Future</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6877,13 +6901,17 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
         <v>59</v>
@@ -6891,11 +6919,11 @@
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
-        <v>46099</v>
+      <c r="A44" s="15" t="n">
+        <v>46100</v>
       </c>
       <c r="B44" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6914,32 +6942,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -6947,13 +6967,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q44" t="n">
         <v>59</v>
@@ -6961,8 +6985,8 @@
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
-        <v>46100</v>
+      <c r="A45" s="15" t="n">
+        <v>46102</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -6984,28 +7008,28 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -7013,26 +7037,22 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/89230f46018b76e4f9b802663c124080_1769803648.webp</t>
-        </is>
-      </c>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q45" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
-        <v>46100</v>
+      <c r="A46" s="15" t="n">
+        <v>46107</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -7059,23 +7079,23 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -7083,33 +7103,29 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/63594afa8c9c063216f1d0e1bcac4b37_1773326960.webp</t>
-        </is>
-      </c>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Q46" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
-        <v>46102</v>
+      <c r="A47" s="15" t="n">
+        <v>46113</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7129,23 +7145,23 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -7153,29 +7169,29 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Q47" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
-        <v>46107</v>
+      <c r="A48" s="15" t="n">
+        <v>46113</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7195,23 +7211,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -7219,21 +7231,21 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q48" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="15" t="n">
         <v>46113</v>
       </c>
       <c r="B49" t="n">
@@ -7256,17 +7268,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -7285,13 +7297,13 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
         <v>59</v>
@@ -7299,7 +7311,7 @@
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="15" t="n">
         <v>46113</v>
       </c>
       <c r="B50" t="n">
@@ -7322,15 +7334,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
@@ -7347,150 +7363,18 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q50" t="n">
         <v>59</v>
       </c>
       <c r="R50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B51" t="n">
-        <v>130</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>59</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B52" t="n">
-        <v>130</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>59</v>
-      </c>
-      <c r="R52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7674,333 +7558,333 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>RELEASE SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>Next 35 Days  ·  51 releases</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Next 35 Days  ·  49 releases</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>STATS AT A GLANCE</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Total Releases</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
-        <v>51</v>
-      </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
+      <c r="B5" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Must Watch</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="21" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
+      <c r="B7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>High Hype</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>High Confidence</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n"/>
+      <c r="B9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Avg Retail Price</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>$201</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Avg Flip %</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>HYPE BREAKDOWN</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>CONFIDENCE BREAKDOWN</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n">
-        <v>1</v>
+      <c r="D14" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>50</v>
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="27" t="n">
         <v>33</v>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>WHERE / RELEASE METHOD</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>App</t>
         </is>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>TOP BRANDS</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="41" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>Nike</t>
         </is>
       </c>
-      <c r="B22" s="42" t="n">
-        <v>21</v>
-      </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="B22" s="39" t="n">
+        <v>23</v>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
         <is>
           <t>████████████████████</t>
         </is>
       </c>
-      <c r="D22" s="24" t="n"/>
+      <c r="D22" s="21" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="41" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>Air Jordan</t>
         </is>
       </c>
-      <c r="B23" s="42" t="n">
-        <v>11</v>
-      </c>
-      <c r="C23" s="43" t="inlineStr">
-        <is>
-          <t>██████████</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="n"/>
+      <c r="B23" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>███████</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="B24" s="42" t="n">
+      <c r="B24" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="C24" s="43" t="inlineStr">
-        <is>
-          <t>████████</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="n"/>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>███████</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>Puma</t>
         </is>
       </c>
-      <c r="B25" s="42" t="n">
+      <c r="B25" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="40" t="inlineStr">
         <is>
           <t>███</t>
         </is>
       </c>
-      <c r="D25" s="24" t="n"/>
+      <c r="D25" s="21" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="41" t="inlineStr">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>Vans</t>
         </is>
       </c>
-      <c r="B26" s="42" t="n">
+      <c r="B26" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="40" t="inlineStr">
         <is>
           <t>███</t>
         </is>
       </c>
-      <c r="D26" s="24" t="n"/>
+      <c r="D26" s="21" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>ASICS</t>
         </is>
       </c>
-      <c r="B27" s="42" t="n">
+      <c r="B27" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="40" t="inlineStr">
         <is>
           <t>██</t>
         </is>
       </c>
-      <c r="D27" s="24" t="n"/>
+      <c r="D27" s="21" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="41" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>Adidas</t>
         </is>
       </c>
-      <c r="B28" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="43" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="n"/>
+      <c r="B28" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>Converse</t>
         </is>
       </c>
-      <c r="B29" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="B29" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>█</t>
         </is>
       </c>
-      <c r="D29" s="24" t="n"/>
+      <c r="D29" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8030,26 +7914,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>How Scores Work</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>HYPE SCORE  (0–100+)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>Brand Tier</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>HIGH brands (Air Jordan, Nike, Yeezy, New Balance, Adidas): +12 pts
 MID brands (Vans, Converse, Puma, Reebok, ASICS, Saucony, Hoka, Salomon): +7 pts
@@ -8058,96 +7942,96 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Collab</t>
         </is>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Any collab keyword (Travis Scott, Off-White, Supreme, Bad Bunny, Kith…): +20 pts</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Limited / Rare</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Limited, Exclusive, QS, PE, Raffle, Friends &amp; Family, Sample…: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Hot Model</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Jordan 1–13, Dunk, Air Max, Kobe, Yeezy Boost, Samba, NB 550/990…: +12 pts</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>Retro / Heritage</t>
         </is>
       </c>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>Retro, OG, Original, Vintage, Heritage: +4 pts</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Price Signal</t>
         </is>
       </c>
-      <c r="B9" s="47" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>Retail ≥ $250 OR retail ≤ $110: +3 pts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Resale Ratio</t>
         </is>
       </c>
-      <c r="B10" s="47" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>Market ÷ Retail ≥ 2.5×: +35 pts  |  ≥ 2.0×: +28  |  ≥ 1.5×: +18  |  ≥ 1.2×: +8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Resale Spread</t>
         </is>
       </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>Market − Retail ≥ $200: +15 pts  |  ≥ $150: +10  |  ≥ $75: +6  |  ≥ $30: +2</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>Hype Level</t>
         </is>
       </c>
-      <c r="B12" s="47" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>HIGH ≥ 42 pts     MED ≥ 20 pts     LOW &lt; 20 pts</t>
         </is>
@@ -8155,103 +8039,103 @@
     </row>
     <row r="13" ht="24" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>CONFIDENCE SCORE  (0–100)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>Primary Source</t>
         </is>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Release confirmed by primary scraper (GOAT): +25 pts</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>Secondary Source</t>
         </is>
       </c>
-      <c r="B16" s="47" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>Confirmed by at least one additional source: +15 pts</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="46" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>Retail Price</t>
         </is>
       </c>
-      <c r="B17" s="47" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>retailPrice field is populated: +15 pts</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="B18" s="47" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>imageUrl field is populated: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>Release URL</t>
         </is>
       </c>
-      <c r="B19" s="47" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>releaseUrl field is populated: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>Source Count</t>
         </is>
       </c>
-      <c r="B20" s="47" t="inlineStr">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>Seen by 3+ sources: +28 pts  |  Seen by 2 sources: +18 pts</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>Single-source cap</t>
         </is>
       </c>
-      <c r="B21" s="47" t="inlineStr">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>Releases seen by only 1 source are capped at 59 (cannot reach HIGH)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="49" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t>Confidence Level</t>
         </is>
       </c>
-      <c r="B22" s="47" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>HIGH ≥ 60 pts     MED ≥ 32 pts     LOW &lt; 32 pts</t>
         </is>
@@ -8259,43 +8143,43 @@
     </row>
     <row r="23" ht="24" customHeight="1"/>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>PRIORITY</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="47" t="inlineStr">
         <is>
           <t>Must Watch</t>
         </is>
       </c>
-      <c r="B25" s="47" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Hype = HIGH  AND  Confidence = HIGH</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="48" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="B26" s="47" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>Hype = HIGH + Confidence = MED, OR Hype = MED + Confidence = HIGH</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="46" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="B27" s="47" t="inlineStr">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>All other hype / confidence combinations</t>
         </is>
@@ -8303,43 +8187,43 @@
     </row>
     <row r="28" ht="24" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>FLIP SCORE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="46" t="inlineStr">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B30" s="47" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>Flip % = round((Market Value − Retail Price) / Retail Price × 100)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="46" t="inlineStr">
+      <c r="A31" s="43" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="B31" s="47" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>$150 retail, $225 market  →  Flip % = +50%  (50% above retail)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="46" t="inlineStr">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>No value</t>
         </is>
       </c>
-      <c r="B32" s="47" t="inlineStr">
+      <c r="B32" s="44" t="inlineStr">
         <is>
           <t>Shown as blank when retail or market value is missing</t>
         </is>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -855,7 +855,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -888,12 +888,12 @@
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>adidas Fear Of God Athletics III</t>
+          <t>adidas HyperBOOST Edge</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr"/>
@@ -907,25 +907,25 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/02/adidas-fear-of-god-athletics-iii-kj5967</t>
+          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>12</v>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -942,15 +942,19 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr">
         <is>
@@ -962,7 +966,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
@@ -974,13 +978,13 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>22</v>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -997,23 +1001,23 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>adidas HyperBOOST Edge</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1021,7 +1025,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -1033,13 +1037,13 @@
       <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>24</v>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1056,17 +1060,17 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+          <t>Thug Club x Converse Chuck 70</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
@@ -1080,16 +1084,18 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+          <t>javascript:void(0)</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="13" t="inlineStr">
@@ -1098,7 +1104,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1106,7 +1112,7 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1115,23 +1121,19 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr"/>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O8" s="6" t="n">
@@ -1139,25 +1141,25 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>7</v>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1174,23 +1176,23 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Thug Club x Converse Chuck 70</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1198,7 +1200,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>javascript:void(0)</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1212,13 +1214,13 @@
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>12</v>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>38</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1235,16 +1237,24 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1255,7 +1265,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -1264,7 +1274,9 @@
       <c r="A11" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
@@ -1273,7 +1285,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1281,7 +1293,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1295,18 +1307,22 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1314,7 +1330,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -1328,13 +1344,13 @@
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>38</v>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1356,19 +1372,15 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1379,7 +1391,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1393,13 +1405,13 @@
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>26</v>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1421,19 +1433,15 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1444,7 +1452,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1464,7 +1472,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1481,17 +1489,17 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr"/>
@@ -1505,7 +1513,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1525,7 +1533,7 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1542,19 +1550,15 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr"/>
       <c r="N15" s="6" t="inlineStr">
         <is>
@@ -1566,7 +1570,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -1580,13 +1584,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>7</v>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1603,20 +1607,24 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1627,7 +1635,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1647,7 +1655,7 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1664,12 +1672,12 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr"/>
@@ -1684,7 +1692,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1704,7 +1712,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1726,19 +1734,15 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1749,7 +1753,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1791,10 +1795,14 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1806,7 +1814,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1826,7 +1834,7 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1848,12 +1856,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, women</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr"/>
@@ -1867,7 +1875,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1909,14 +1917,10 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -1928,7 +1932,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1942,13 +1946,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>22</v>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1970,14 +1974,10 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr"/>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2088,10 +2088,14 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr"/>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2117,13 +2121,13 @@
       </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>12</v>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2145,10 +2149,14 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="inlineStr"/>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -2160,7 +2168,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2174,13 +2182,13 @@
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>12</v>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2202,12 +2210,12 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr"/>
@@ -2221,7 +2229,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2263,7 +2271,7 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
@@ -2282,7 +2290,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2324,7 +2332,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
@@ -2343,7 +2351,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2385,12 +2393,12 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
@@ -2404,7 +2412,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2418,13 +2426,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>24</v>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2446,12 +2454,12 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2465,7 +2473,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2474,18 +2482,16 @@
       <c r="A31" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>210</v>
-      </c>
+      <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>24</v>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2493,7 +2499,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2507,18 +2513,18 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O31" s="6" t="n">
@@ -2526,7 +2532,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2546,7 +2552,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2563,12 +2569,12 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
@@ -2587,7 +2593,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -2596,7 +2602,9 @@
       <c r="A33" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="13" t="inlineStr">
@@ -2605,7 +2613,7 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2622,23 +2630,19 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -2646,7 +2650,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -2688,14 +2692,10 @@
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
@@ -2749,10 +2749,14 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr">
         <is>
@@ -2764,7 +2768,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -2801,12 +2805,12 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
@@ -2825,7 +2829,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -3266,10 +3270,14 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M44" s="6" t="inlineStr"/>
       <c r="N44" s="6" t="inlineStr">
         <is>
@@ -3281,7 +3289,7 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
@@ -3301,7 +3309,7 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3318,24 +3326,20 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr"/>
       <c r="N45" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3346,25 +3350,27 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>32</v>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3381,23 +3387,23 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr"/>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3405,25 +3411,27 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="n">
-        <v>32</v>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3440,23 +3448,19 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -3464,25 +3468,27 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>34</v>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3490,7 +3496,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3499,23 +3505,27 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -3523,7 +3533,7 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
@@ -3535,13 +3545,13 @@
       <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>12</v>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3549,7 +3559,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
@@ -3563,10 +3573,14 @@
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr"/>
+          <t>Fragment Design x Nike Book 2</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
         <is>
@@ -3578,7 +3592,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
@@ -3590,13 +3604,13 @@
       <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>12</v>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3604,7 +3618,7 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3618,10 +3632,14 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr"/>
+          <t>Fragment Design x Nike Mind 001</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
@@ -3633,14 +3651,14 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr"/>
@@ -3651,7 +3669,7 @@
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3668,23 +3686,23 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>Nike Air Max 90 QS</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, running, exclusive</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -3692,25 +3710,25 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr"/>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="n">
-        <v>28</v>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3718,7 +3736,7 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
@@ -3727,23 +3745,19 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr"/>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -3751,25 +3765,25 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46104</v>
+        <v>46100</v>
       </c>
       <c r="B53" s="5" t="inlineStr"/>
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="6" t="inlineStr"/>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>24</v>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
@@ -3777,7 +3791,7 @@
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
@@ -3791,18 +3805,14 @@
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -3810,14 +3820,14 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46107</v>
+        <v>46102</v>
       </c>
       <c r="B54" s="5" t="inlineStr"/>
       <c r="C54" s="5" t="inlineStr"/>
@@ -3828,7 +3838,7 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
@@ -3845,17 +3855,17 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr"/>
@@ -3869,27 +3879,25 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46102</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr"/>
       <c r="C55" s="5" t="inlineStr"/>
       <c r="D55" s="6" t="inlineStr"/>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>16</v>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
@@ -3897,7 +3905,7 @@
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
@@ -3911,18 +3919,18 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Shoes Air Jordan 14 Retro</t>
         </is>
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
@@ -3930,27 +3938,25 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46104</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr"/>
       <c r="C56" s="5" t="inlineStr"/>
       <c r="D56" s="6" t="inlineStr"/>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>12</v>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
@@ -3958,7 +3964,7 @@
         </is>
       </c>
       <c r="H56" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
@@ -3972,14 +3978,18 @@
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L56" s="12" t="inlineStr"/>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M56" s="6" t="inlineStr"/>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
@@ -3987,27 +3997,25 @@
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
         </is>
       </c>
       <c r="Q56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46107</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr"/>
       <c r="C57" s="5" t="inlineStr"/>
       <c r="D57" s="6" t="inlineStr"/>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>7</v>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
@@ -4015,7 +4023,7 @@
         </is>
       </c>
       <c r="H57" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
@@ -4024,23 +4032,23 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O57" s="6" t="n">
@@ -4048,7 +4056,7 @@
       </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q57" s="12" t="inlineStr"/>
@@ -4068,7 +4076,7 @@
         </is>
       </c>
       <c r="F58" s="14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
@@ -4085,17 +4093,17 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr"/>
@@ -4109,10 +4117,189 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q58" s="12" t="inlineStr"/>
+      <c r="Q61" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4129,13 +4316,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="67" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -4187,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4210,29 +4397,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-16T19:37:34Z</t>
+          <t>2026-03-17T07:39:28Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>adidas HyperBOOST Edge</t>
+          <t>Jacquemus x Nike Moon Shoe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -4240,7 +4427,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-16T19:37:34Z</t>
+          <t>2026-03-17T07:39:28Z</t>
         </is>
       </c>
     </row>
@@ -4252,17 +4439,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thug Club x Converse Chuck 70</t>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -4270,7 +4457,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-16T19:37:34Z</t>
+          <t>2026-03-17T07:39:28Z</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4474,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -4300,7 +4487,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-16T19:37:34Z</t>
+          <t>2026-03-17T07:39:28Z</t>
         </is>
       </c>
     </row>
@@ -4312,17 +4499,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -4330,7 +4517,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-16T19:37:34Z</t>
+          <t>2026-03-17T07:39:28Z</t>
         </is>
       </c>
     </row>
@@ -4342,17 +4529,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -4360,7 +4547,37 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-16T19:37:34Z</t>
+          <t>2026-03-17T07:39:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-17T07:39:28Z</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4492,7 +4709,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -4519,12 +4736,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>adidas Fear Of God Athletics III</t>
+          <t>adidas HyperBOOST Edge</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -4543,13 +4760,13 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/02/adidas-fear-of-god-athletics-iii-kj5967</t>
+          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
         <v>50</v>
@@ -4558,14 +4775,14 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4580,15 +4797,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -4605,20 +4826,16 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/2606b3ba58d54a083c894b52edcd3cad_1773072526.webp</t>
-        </is>
-      </c>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
@@ -4631,7 +4848,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4646,28 +4863,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>adidas HyperBOOST Edge</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -4675,13 +4892,13 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
         <v>50</v>
@@ -4697,7 +4914,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4712,17 +4929,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+          <t>Thug Club x Converse Chuck 70</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4741,13 +4958,13 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+          <t>javascript:void(0)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
         <v>50</v>
@@ -4756,10 +4973,10 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4778,28 +4995,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -4807,29 +5020,29 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4844,28 +5057,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thug Club x Converse Chuck 70</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4873,13 +5086,13 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>javascript:void(0)</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="n">
         <v>50</v>
@@ -4895,7 +5108,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4910,16 +5123,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4935,13 +5156,13 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
         <v>59</v>
@@ -4953,7 +5174,7 @@
         <v>46099</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4977,23 +5198,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -5001,16 +5226,16 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
@@ -5023,7 +5248,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5043,19 +5268,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5071,13 +5292,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -5093,7 +5314,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5113,19 +5334,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5141,13 +5358,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -5178,17 +5395,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -5207,13 +5424,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -5244,19 +5461,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
@@ -5273,13 +5486,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -5295,7 +5508,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5310,20 +5523,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5339,13 +5556,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -5376,12 +5593,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -5401,13 +5618,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -5443,19 +5660,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5471,13 +5684,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -5513,10 +5726,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
@@ -5533,7 +5750,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -5575,12 +5792,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>hot-model, running, women</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -5599,13 +5816,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -5641,14 +5858,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -5665,7 +5878,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -5687,7 +5900,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5707,14 +5920,10 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -5731,13 +5940,13 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
         <v>59</v>
@@ -5773,7 +5982,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -5793,7 +6002,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -5835,10 +6044,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -5855,7 +6068,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5877,7 +6090,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5897,10 +6110,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -5917,13 +6134,13 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -5939,7 +6156,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5959,12 +6176,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -5983,13 +6200,13 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
         <v>59</v>
@@ -6025,7 +6242,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6049,7 +6266,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -6091,7 +6308,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6115,7 +6332,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -6157,12 +6374,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -6181,7 +6398,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6203,7 +6420,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6223,12 +6440,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -6247,13 +6464,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -6265,11 +6482,11 @@
         <v>46099</v>
       </c>
       <c r="B29" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6289,23 +6506,23 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -6313,16 +6530,16 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R29" t="inlineStr"/>
     </row>
@@ -6350,12 +6567,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6379,13 +6596,13 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
         <v>59</v>
@@ -6397,7 +6614,7 @@
         <v>46099</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6416,28 +6633,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -6445,17 +6658,13 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/4a1c66575467445342b9085cc4510900_1772681368.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
         <v>59</v>
@@ -6491,14 +6700,10 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -6515,7 +6720,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -6557,10 +6762,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
@@ -6577,7 +6786,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -6614,12 +6823,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6643,7 +6852,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -7119,10 +7328,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
@@ -7139,7 +7352,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -7176,24 +7389,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -7209,13 +7418,13 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
         <v>59</v>
@@ -7224,14 +7433,14 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7246,28 +7455,28 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>collab</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -7275,17 +7484,13 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/89230f46018b76e4f9b802663c124080_1769803648.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
         <v>59</v>
@@ -7294,14 +7499,14 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7316,28 +7521,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -7345,17 +7546,13 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/63594afa8c9c063216f1d0e1bcac4b37_1773326960.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
         <v>59</v>
@@ -7364,14 +7561,14 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7386,28 +7583,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -7415,16 +7616,16 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R46" t="inlineStr"/>
     </row>
@@ -7437,7 +7638,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7457,10 +7658,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Fragment Design x Nike Book 2</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
@@ -7477,20 +7682,16 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
-        </is>
-      </c>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="Q47" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
@@ -7503,7 +7704,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7523,10 +7724,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Fragment Design x Nike Mind 001</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
@@ -7543,26 +7748,22 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
-        </is>
-      </c>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="Q48" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
@@ -7584,28 +7785,28 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>Nike Air Max 90 QS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, running, exclusive</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -7613,13 +7814,13 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Q49" t="n">
         <v>50</v>
@@ -7628,14 +7829,14 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7650,28 +7851,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7679,29 +7876,33 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Q50" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46104</v>
+        <v>46100</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7721,23 +7922,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7745,22 +7942,26 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q51" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46107</v>
+        <v>46102</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -7782,17 +7983,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7811,13 +8012,13 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q52" t="n">
         <v>50</v>
@@ -7826,14 +8027,14 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46113</v>
+        <v>46102</v>
       </c>
       <c r="B53" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7853,23 +8054,23 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Shoes Air Jordan 14 Retro</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7877,29 +8078,29 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q53" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46113</v>
+        <v>46104</v>
       </c>
       <c r="B54" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7919,19 +8120,23 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7939,29 +8144,29 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q54" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B55" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7976,28 +8181,28 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -8005,16 +8210,16 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q55" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R55" t="inlineStr"/>
     </row>
@@ -8042,17 +8247,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8071,18 +8276,212 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q56" t="n">
         <v>59</v>
       </c>
       <c r="R56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B57" t="n">
+        <v>130</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>59</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B58" t="n">
+        <v>130</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>59</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B59" t="n">
+        <v>130</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>59</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8256,7 +8655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8275,7 +8674,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  55 releases</t>
+          <t>Next 35 Days  ·  58 releases</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8692,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -8354,7 +8753,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$202</t>
+          <t>$203</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -8411,7 +8810,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -8419,7 +8818,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8429,7 +8828,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -8473,7 +8872,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -8485,15 +8884,15 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>███████</t>
+          <t>█████████</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>
@@ -8501,15 +8900,15 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B24" s="39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>██████</t>
+          <t>████████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -8517,15 +8916,15 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="38" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B25" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D25" s="21" t="n"/>
@@ -8533,7 +8932,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B26" s="39" t="n">
@@ -8549,11 +8948,11 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B27" s="39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
@@ -8565,7 +8964,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B28" s="39" t="n">
@@ -8593,6 +8992,22 @@
         </is>
       </c>
       <c r="D29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>Saucony</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -744,7 +744,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="11" max="11"/>
-    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -1649,13 +1649,13 @@
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>12</v>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>34</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1677,11 +1677,19 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1692,7 +1700,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1706,13 +1714,13 @@
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>24</v>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1734,14 +1742,10 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1767,13 +1771,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>12</v>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1795,12 +1799,12 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
@@ -1814,7 +1818,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1828,13 +1832,13 @@
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>22</v>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1856,12 +1860,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr"/>
@@ -1875,7 +1879,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1889,13 +1893,13 @@
       </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>12</v>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1917,10 +1921,14 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -1932,7 +1940,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1974,7 +1982,7 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr"/>
@@ -1989,7 +1997,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2031,7 +2039,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2046,7 +2054,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2088,14 +2096,10 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2107,7 +2111,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2121,13 +2125,13 @@
       </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>24</v>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2149,12 +2153,12 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
@@ -2168,7 +2172,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2210,7 +2214,7 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
@@ -2229,7 +2233,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2271,7 +2275,7 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2332,7 +2336,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
@@ -2351,7 +2355,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2393,12 +2397,12 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
@@ -2412,7 +2416,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2426,13 +2430,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>12</v>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2454,12 +2458,12 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2473,7 +2477,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2482,7 +2486,9 @@
       <c r="A31" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="13" t="inlineStr">
@@ -2499,7 +2505,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2513,18 +2519,18 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O31" s="6" t="n">
@@ -2532,7 +2538,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2541,9 +2547,7 @@
       <c r="A32" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>210</v>
-      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="13" t="inlineStr">
@@ -2552,7 +2556,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2560,7 +2564,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2569,23 +2573,23 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O32" s="6" t="n">
@@ -2593,7 +2597,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -2635,10 +2639,14 @@
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr"/>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
@@ -2650,7 +2658,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -2692,7 +2700,7 @@
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr"/>
@@ -2749,14 +2757,10 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr">
         <is>
@@ -2768,7 +2772,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -2805,12 +2809,12 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Saucony</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
@@ -2829,7 +2833,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -2849,7 +2853,7 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2866,15 +2870,19 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
@@ -2886,7 +2894,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -2928,7 +2936,7 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr"/>
@@ -2943,7 +2951,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -2985,7 +2993,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr"/>
@@ -3000,7 +3008,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -3042,7 +3050,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
@@ -3057,7 +3065,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -3099,7 +3107,7 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr"/>
@@ -3114,7 +3122,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
@@ -3156,7 +3164,7 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr"/>
@@ -3171,7 +3179,7 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
@@ -3213,7 +3221,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr"/>
@@ -3228,7 +3236,7 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
@@ -3270,14 +3278,10 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr"/>
       <c r="N44" s="6" t="inlineStr">
         <is>
@@ -3289,7 +3293,7 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
@@ -3331,7 +3335,7 @@
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
@@ -3350,7 +3354,7 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
@@ -3392,12 +3396,12 @@
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr"/>
@@ -3411,7 +3415,7 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
@@ -3453,10 +3457,14 @@
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
@@ -3468,7 +3476,7 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
@@ -3488,7 +3496,7 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3505,24 +3513,16 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3533,25 +3533,27 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="n">
-        <v>32</v>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3559,7 +3561,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
@@ -3568,23 +3570,27 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>collab</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -3592,7 +3598,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
@@ -3632,7 +3638,7 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="L50" s="12" t="inlineStr">
@@ -3651,7 +3657,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
@@ -3669,7 +3675,7 @@
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3691,12 +3697,12 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
@@ -3710,7 +3716,7 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
@@ -3722,13 +3728,13 @@
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr"/>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>12</v>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>34</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3736,7 +3742,7 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
@@ -3750,10 +3756,14 @@
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr"/>
+          <t>Nike Air Max 90 QS</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
       <c r="M52" s="6" t="inlineStr"/>
       <c r="N52" s="6" t="inlineStr">
         <is>
@@ -3765,7 +3775,7 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
@@ -3805,7 +3815,7 @@
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
+          <t>Nike GT Future</t>
         </is>
       </c>
       <c r="L53" s="12" t="inlineStr"/>
@@ -3820,25 +3830,25 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B54" s="5" t="inlineStr"/>
       <c r="C54" s="5" t="inlineStr"/>
       <c r="D54" s="6" t="inlineStr"/>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>28</v>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
@@ -3846,7 +3856,7 @@
         </is>
       </c>
       <c r="H54" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
@@ -3855,23 +3865,19 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr"/>
       <c r="M54" s="6" t="inlineStr"/>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O54" s="6" t="n">
@@ -3879,7 +3885,7 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
@@ -3919,12 +3925,12 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
@@ -3945,7 +3951,7 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>46104</v>
+        <v>46102</v>
       </c>
       <c r="B56" s="5" t="inlineStr"/>
       <c r="C56" s="5" t="inlineStr"/>
@@ -3956,7 +3962,7 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
@@ -3973,17 +3979,17 @@
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>Shoes Air Jordan 14 Retro</t>
         </is>
       </c>
       <c r="L56" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr"/>
@@ -3997,14 +4003,14 @@
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B57" s="5" t="inlineStr"/>
       <c r="C57" s="5" t="inlineStr"/>
@@ -4037,12 +4043,12 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
         </is>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
@@ -4056,27 +4062,25 @@
       </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
         </is>
       </c>
       <c r="Q57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46107</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr"/>
       <c r="C58" s="5" t="inlineStr"/>
       <c r="D58" s="6" t="inlineStr"/>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>16</v>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
@@ -4084,7 +4088,7 @@
         </is>
       </c>
       <c r="H58" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
@@ -4093,23 +4097,23 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr"/>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O58" s="6" t="n">
@@ -4117,7 +4121,7 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q58" s="12" t="inlineStr"/>
@@ -4137,7 +4141,7 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
@@ -4154,15 +4158,19 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L59" s="12" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="M59" s="6" t="inlineStr"/>
       <c r="N59" s="6" t="inlineStr">
         <is>
@@ -4174,7 +4182,7 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q59" s="12" t="inlineStr"/>
@@ -4194,7 +4202,7 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
@@ -4211,19 +4219,15 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L60" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr"/>
       <c r="M60" s="6" t="inlineStr"/>
       <c r="N60" s="6" t="inlineStr">
         <is>
@@ -4235,7 +4239,7 @@
       </c>
       <c r="P60" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q60" s="12" t="inlineStr"/>
@@ -4277,7 +4281,7 @@
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="L61" s="12" t="inlineStr">
@@ -4296,10 +4300,71 @@
       </c>
       <c r="P61" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L62" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" s="12" t="inlineStr">
+        <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q61" s="12" t="inlineStr"/>
+      <c r="Q62" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4316,13 +4381,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="67" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -4374,22 +4439,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas Fear Of God Athletics III</t>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -4397,187 +4462,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-17T07:39:28Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-17T07:39:28Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-17T07:39:28Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Saucony</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-17T07:39:28Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-17T07:39:28Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-17T07:39:28Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-17T07:39:28Z</t>
+          <t>2026-03-17T19:39:04Z</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4602,7 +4487,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="54" customWidth="1" min="11" max="11"/>
@@ -5578,7 +5463,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5598,11 +5483,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5618,13 +5511,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -5640,7 +5533,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5660,14 +5553,10 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
@@ -5684,13 +5573,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -5706,7 +5595,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5726,12 +5615,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -5750,13 +5639,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -5772,7 +5661,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5792,12 +5681,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -5816,13 +5705,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -5838,7 +5727,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5858,10 +5747,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -5878,13 +5771,13 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q19" t="n">
         <v>59</v>
@@ -5920,7 +5813,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -5940,7 +5833,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -5982,7 +5875,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -6002,7 +5895,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -6044,14 +5937,10 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -6068,7 +5957,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -6090,7 +5979,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6110,12 +5999,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -6134,13 +6023,13 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -6176,7 +6065,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6200,7 +6089,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -6242,7 +6131,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6266,7 +6155,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -6308,7 +6197,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6332,7 +6221,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -6374,12 +6263,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -6398,7 +6287,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6420,7 +6309,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6440,12 +6329,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -6464,13 +6353,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -6482,7 +6371,7 @@
         <v>46099</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6506,23 +6395,23 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -6530,7 +6419,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -6539,7 +6428,7 @@
         <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R29" t="inlineStr"/>
     </row>
@@ -6548,7 +6437,7 @@
         <v>46099</v>
       </c>
       <c r="B30" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6567,28 +6456,28 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -6596,16 +6485,16 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q30" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
@@ -6638,10 +6527,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
@@ -6658,7 +6551,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -6700,7 +6593,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -6762,14 +6655,10 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
@@ -6786,7 +6675,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -6823,12 +6712,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Saucony</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6852,7 +6741,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -6889,15 +6778,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
@@ -6914,13 +6807,13 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
         <v>59</v>
@@ -6956,7 +6849,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6976,7 +6869,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -7018,7 +6911,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -7038,7 +6931,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -7080,7 +6973,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -7100,7 +6993,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -7142,7 +7035,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -7162,7 +7055,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -7204,7 +7097,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -7224,7 +7117,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -7266,7 +7159,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -7286,7 +7179,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -7328,14 +7221,10 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
@@ -7352,7 +7241,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -7394,7 +7283,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7418,7 +7307,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -7460,12 +7349,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -7484,7 +7373,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -7526,10 +7415,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
@@ -7546,7 +7439,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -7583,24 +7476,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -7616,13 +7501,13 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
         <v>59</v>
@@ -7631,14 +7516,14 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7653,28 +7538,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>collab</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -7682,16 +7571,16 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Q47" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
@@ -7724,7 +7613,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7748,7 +7637,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -7790,12 +7679,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -7814,13 +7703,13 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q49" t="n">
         <v>50</v>
@@ -7836,7 +7725,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7856,10 +7745,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Nike Air Max 90 QS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
@@ -7876,20 +7769,16 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
-        </is>
-      </c>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="Q50" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R50" t="inlineStr"/>
     </row>
@@ -7922,7 +7811,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
+          <t>Nike GT Future</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -7942,12 +7831,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
@@ -7961,14 +7850,14 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7983,28 +7872,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -8012,16 +7897,20 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Q52" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R52" t="inlineStr"/>
     </row>
@@ -8054,12 +7943,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -8093,7 +7982,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46104</v>
+        <v>46102</v>
       </c>
       <c r="B54" t="n">
         <v>0</v>
@@ -8115,17 +8004,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>Shoes Air Jordan 14 Retro</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -8144,13 +8033,13 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q54" t="n">
         <v>50</v>
@@ -8159,7 +8048,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
@@ -8186,12 +8075,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8210,7 +8099,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -8225,14 +8114,14 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B56" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8247,28 +8136,28 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -8276,16 +8165,16 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q56" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R56" t="inlineStr"/>
     </row>
@@ -8313,15 +8202,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
@@ -8338,13 +8231,13 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q57" t="n">
         <v>59</v>
@@ -8375,19 +8268,15 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
@@ -8404,13 +8293,13 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q58" t="n">
         <v>59</v>
@@ -8446,7 +8335,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8470,7 +8359,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8482,6 +8371,72 @@
         <v>59</v>
       </c>
       <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B60" t="n">
+        <v>130</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>59</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8674,7 +8629,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  58 releases</t>
+          <t>Next 35 Days  ·  59 releases</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8647,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -8810,7 +8765,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -8818,7 +8773,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8853,7 +8808,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -8872,7 +8827,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -8908,7 +8863,7 @@
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>████████</t>
+          <t>███████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -3667,13 +3667,13 @@
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr"/>
       <c r="D51" s="6" t="inlineStr"/>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="n">
-        <v>12</v>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>22</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
@@ -3714,18 +3714,16 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46108</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr"/>
       <c r="E52" s="7" t="inlineStr">
@@ -3734,7 +3732,7 @@
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3742,7 +3740,7 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
@@ -3751,23 +3749,23 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr"/>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -3775,27 +3773,25 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46109</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="6" t="inlineStr"/>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>12</v>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
@@ -3803,7 +3799,7 @@
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
@@ -3812,19 +3808,23 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr"/>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
@@ -3869,17 +3869,17 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="F55" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
@@ -3930,19 +3930,15 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L55" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr"/>
       <c r="M55" s="6" t="inlineStr"/>
       <c r="N55" s="6" t="inlineStr">
         <is>
@@ -3954,10 +3950,132 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q55" s="12" t="inlineStr"/>
+      <c r="Q57" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3974,13 +4092,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -4032,22 +4150,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -4055,19 +4173,19 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-19T07:32:54Z</t>
+          <t>2026-03-19T18:10:06Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4077,7 +4195,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -4085,1297 +4203,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Saucony</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>App entry Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-19T07:32:54Z</t>
+          <t>2026-03-19T18:10:06Z</t>
         </is>
       </c>
     </row>
@@ -5390,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8584,7 +7412,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8604,12 +7432,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8628,13 +7456,13 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q49" t="n">
         <v>50</v>
@@ -8643,10 +7471,10 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="B50" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -8665,28 +7493,28 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -8694,29 +7522,29 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q50" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B51" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8731,24 +7559,28 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -8756,16 +7588,16 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q51" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R51" t="inlineStr"/>
     </row>
@@ -8793,17 +7625,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8822,13 +7654,13 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q52" t="n">
         <v>59</v>
@@ -8859,19 +7691,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
@@ -8888,18 +7716,150 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q53" t="n">
         <v>59</v>
       </c>
       <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B54" t="n">
+        <v>130</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>59</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" t="n">
+        <v>130</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>59</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9092,7 +8052,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  52 releases</t>
+          <t>Next 35 Days  ·  54 releases</t>
         </is>
       </c>
     </row>
@@ -9110,7 +8070,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -9228,7 +8188,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -9236,7 +8196,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -9290,7 +8250,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -9322,11 +8282,11 @@
         </is>
       </c>
       <c r="B24" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>████</t>
+          <t>█████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -1636,17 +1636,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1688,96 +1688,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-22T06:34:29Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Shoes Air Jordan 14 Retro</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-22T06:34:29Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-22T06:34:29Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -855,9 +855,11 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46104</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
@@ -866,7 +868,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -874,7 +876,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -883,23 +885,27 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -907,7 +913,7 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
@@ -927,7 +933,7 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -949,15 +955,19 @@
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -968,7 +978,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
@@ -982,13 +992,13 @@
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>16</v>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -1010,12 +1020,12 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
@@ -1029,7 +1039,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -1110,7 +1120,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1127,17 +1137,17 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr"/>
@@ -1151,7 +1161,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -1193,10 +1203,14 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
@@ -1208,7 +1222,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1222,13 +1236,13 @@
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>34</v>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1245,24 +1259,16 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, women, exclusive</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1273,7 +1279,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -1287,13 +1293,13 @@
       </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>12</v>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1315,11 +1321,19 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1350,7 +1364,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1372,15 +1386,19 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr"/>
+          <t>hot-model, running, women, exclusive</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1391,7 +1409,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1405,13 +1423,13 @@
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>12</v>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1433,15 +1451,19 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1466,13 +1488,13 @@
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>24</v>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1494,14 +1516,10 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, kids</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -1513,7 +1531,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1555,12 +1573,12 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
@@ -1574,7 +1592,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -1594,7 +1612,7 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1611,12 +1629,12 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
@@ -1635,7 +1653,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1655,7 +1673,7 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1672,15 +1690,19 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr"/>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="inlineStr"/>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -1692,7 +1714,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1706,13 +1728,13 @@
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>3</v>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1729,15 +1751,19 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr"/>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, kids</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -1749,7 +1775,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1763,13 +1789,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>3</v>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1786,15 +1812,19 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr"/>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, kids</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1806,7 +1836,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1826,7 +1856,7 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1843,15 +1873,19 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr"/>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -1863,7 +1897,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1883,7 +1917,7 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1900,12 +1934,12 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr"/>
@@ -1920,7 +1954,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1962,7 +1996,7 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr"/>
@@ -1977,7 +2011,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2019,7 +2053,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2034,7 +2068,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2076,7 +2110,7 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr"/>
@@ -2091,7 +2125,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2133,7 +2167,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
@@ -2148,25 +2182,27 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>24</v>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2174,7 +2210,7 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2183,23 +2219,19 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr"/>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O26" s="6" t="n">
@@ -2207,25 +2239,27 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>24</v>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2233,7 +2267,7 @@
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
@@ -2242,23 +2276,19 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr"/>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O27" s="6" t="n">
@@ -2266,25 +2296,27 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>24</v>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -2292,7 +2324,7 @@
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -2301,23 +2333,19 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr"/>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O28" s="6" t="n">
@@ -2325,25 +2353,27 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>22</v>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2351,7 +2381,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2360,23 +2390,19 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr"/>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2384,25 +2410,25 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>12</v>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2424,12 +2450,12 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2443,14 +2469,14 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46109</v>
+        <v>46107</v>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
@@ -2461,7 +2487,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2478,17 +2504,17 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
@@ -2502,14 +2528,14 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46112</v>
+        <v>46107</v>
       </c>
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
@@ -2542,12 +2568,12 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
@@ -2561,27 +2587,25 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46108</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>16</v>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2589,7 +2613,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2598,23 +2622,23 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -2622,18 +2646,16 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46108</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="13" t="inlineStr">
@@ -2650,7 +2672,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2659,19 +2681,23 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O34" s="6" t="n">
@@ -2679,27 +2705,25 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46109</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>16</v>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2707,7 +2731,7 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
@@ -2721,18 +2745,18 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O35" s="6" t="n">
@@ -2740,18 +2764,16 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46109</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="13" t="inlineStr">
@@ -2760,7 +2782,7 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2768,7 +2790,7 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
@@ -2782,18 +2804,14 @@
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr"/>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
@@ -2801,27 +2819,25 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>12</v>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2829,7 +2845,7 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
@@ -2843,14 +2859,18 @@
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr"/>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
@@ -2858,7 +2878,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -2878,7 +2898,7 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -2895,17 +2915,17 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr"/>
@@ -2919,7 +2939,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -2939,7 +2959,7 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
@@ -2956,19 +2976,15 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr"/>
       <c r="N39" s="6" t="inlineStr">
         <is>
@@ -2980,7 +2996,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -3000,7 +3016,7 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
@@ -3017,17 +3033,17 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr"/>
@@ -3041,7 +3057,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -3051,7 +3067,7 @@
         <v>46113</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
@@ -3061,7 +3077,7 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -3078,17 +3094,17 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr"/>
@@ -3102,25 +3118,27 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>24</v>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -3128,7 +3146,7 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -3142,29 +3160,328 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr"/>
       <c r="N42" s="6" t="inlineStr">
         <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+        </is>
+      </c>
+      <c r="Q43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="O42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" s="12" t="inlineStr">
+      <c r="O47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
-      <c r="Q42" s="12" t="inlineStr"/>
+      <c r="Q47" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3181,10 +3498,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -3239,22 +3556,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3262,7 +3579,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-23T18:11:17Z</t>
+          <t>2026-03-24T07:39:40Z</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3596,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -3292,7 +3609,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-23T18:11:17Z</t>
+          <t>2026-03-24T07:39:40Z</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3631,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -3322,7 +3639,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-23T18:11:17Z</t>
+          <t>2026-03-24T07:39:40Z</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3656,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -3352,7 +3669,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-23T18:11:17Z</t>
+          <t>2026-03-24T07:39:40Z</t>
         </is>
       </c>
     </row>
@@ -3369,12 +3686,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -3382,7 +3699,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-23T18:11:17Z</t>
+          <t>2026-03-24T07:39:40Z</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3716,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -3412,7 +3729,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-23T18:11:17Z</t>
+          <t>2026-03-24T07:39:40Z</t>
         </is>
       </c>
     </row>
@@ -3424,17 +3741,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -3442,703 +3759,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-23T18:11:17Z</t>
+          <t>2026-03-24T07:39:40Z</t>
         </is>
       </c>
     </row>
@@ -4153,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4270,10 +3891,10 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4292,28 +3913,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -4321,16 +3946,16 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
@@ -4363,15 +3988,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4387,13 +4016,13 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
         <v>59</v>
@@ -4409,7 +4038,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4429,12 +4058,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4453,13 +4082,13 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
         <v>59</v>
@@ -4556,17 +4185,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -4585,13 +4214,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
         <v>59</v>
@@ -4627,10 +4256,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -4647,7 +4280,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -4669,7 +4302,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4684,24 +4317,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>hot-model, running, women, exclusive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4717,13 +4342,13 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="n">
         <v>59</v>
@@ -4739,7 +4364,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4759,11 +4384,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4785,7 +4418,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>59</v>
@@ -4821,15 +4454,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>hot-model, running, women, exclusive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4845,13 +4482,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -4867,7 +4504,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4887,15 +4524,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4917,7 +4558,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -4933,7 +4574,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4953,14 +4594,10 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>hot-model, running, kids</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -4977,13 +4614,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -5019,12 +4656,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -5043,7 +4680,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -5080,12 +4717,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5109,13 +4746,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -5146,15 +4783,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
@@ -5171,13 +4812,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -5193,7 +4834,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5208,15 +4849,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>hot-model, running, kids</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
@@ -5233,13 +4878,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -5255,7 +4900,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5270,15 +4915,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>hot-model, running, kids</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
@@ -5295,13 +4944,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -5332,15 +4981,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -5357,13 +5010,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -5394,12 +5047,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -5419,13 +5072,13 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
         <v>59</v>
@@ -5461,7 +5114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -5481,7 +5134,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -5523,7 +5176,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -5543,7 +5196,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -5585,7 +5238,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -5605,7 +5258,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5647,7 +5300,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -5667,7 +5320,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -5682,14 +5335,14 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5704,28 +5357,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5733,29 +5382,29 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5770,28 +5419,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -5799,29 +5444,29 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5836,28 +5481,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -5865,29 +5506,29 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46108</v>
+        <v>46105</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5902,28 +5543,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5931,29 +5568,29 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5973,12 +5610,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -5997,13 +5634,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q28" t="n">
         <v>50</v>
@@ -6012,7 +5649,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46109</v>
+        <v>46107</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -6034,17 +5671,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -6063,13 +5700,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q29" t="n">
         <v>50</v>
@@ -6078,7 +5715,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46112</v>
+        <v>46107</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -6105,12 +5742,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -6129,7 +5766,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -6144,14 +5781,14 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="B31" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6166,28 +5803,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -6195,25 +5832,25 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="B32" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6232,24 +5869,28 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -6257,7 +5898,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -6266,20 +5907,20 @@
         <v>12</v>
       </c>
       <c r="Q32" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B33" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6299,23 +5940,23 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -6323,25 +5964,25 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q33" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B34" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6365,23 +6006,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -6389,29 +6026,29 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q34" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="B35" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6431,19 +6068,23 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -6451,16 +6092,16 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q35" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R35" t="inlineStr"/>
     </row>
@@ -6488,17 +6129,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -6517,13 +6158,13 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q36" t="n">
         <v>59</v>
@@ -6554,19 +6195,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
@@ -6583,13 +6220,13 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q37" t="n">
         <v>59</v>
@@ -6620,17 +6257,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -6649,13 +6286,13 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q38" t="n">
         <v>59</v>
@@ -6667,7 +6304,7 @@
         <v>46113</v>
       </c>
       <c r="B39" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6686,17 +6323,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -6715,13 +6352,13 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q39" t="n">
         <v>59</v>
@@ -6730,14 +6367,14 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6757,23 +6394,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6781,18 +6414,348 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>59</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B41" t="n">
+        <v>150</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>59</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B42" t="n">
+        <v>150</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>59</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B43" t="n">
+        <v>150</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>59</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B44" t="n">
+        <v>130</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>59</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
         <v>24</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q45" t="n">
         <v>50</v>
       </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6985,7 +6948,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  39 releases</t>
+          <t>Next 35 Days  ·  44 releases</t>
         </is>
       </c>
     </row>
@@ -7003,7 +6966,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -7064,7 +7027,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$160</t>
+          <t>$161</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -7121,7 +7084,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -7129,7 +7092,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -7139,7 +7102,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -7164,7 +7127,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -7183,7 +7146,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -7199,11 +7162,11 @@
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>██████████</t>
+          <t>████████████</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>
@@ -7219,7 +7182,7 @@
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>██████████</t>
+          <t>█████████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -7235,7 +7198,7 @@
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>████</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D25" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -2419,7 +2419,9 @@
       <c r="A30" s="4" t="n">
         <v>46107</v>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
@@ -2428,7 +2430,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2436,7 +2438,7 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2445,23 +2447,27 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O30" s="6" t="n">
@@ -2469,7 +2475,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2478,7 +2484,9 @@
       <c r="A31" s="4" t="n">
         <v>46107</v>
       </c>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
@@ -2487,7 +2495,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2495,7 +2503,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2504,23 +2512,27 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O31" s="6" t="n">
@@ -2528,7 +2540,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2537,16 +2549,18 @@
       <c r="A32" s="4" t="n">
         <v>46107</v>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>24</v>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2554,7 +2568,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2563,23 +2577,23 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O32" s="6" t="n">
@@ -2587,25 +2601,27 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr"/>
+        <v>46107</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>22</v>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2613,7 +2629,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2622,23 +2638,23 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -2646,16 +2662,18 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr"/>
+        <v>46107</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="13" t="inlineStr">
@@ -2664,7 +2682,7 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2672,7 +2690,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2681,12 +2699,12 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
@@ -2697,7 +2715,7 @@
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O34" s="6" t="n">
@@ -2705,25 +2723,27 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr"/>
+        <v>46107</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>28</v>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2731,7 +2751,7 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
@@ -2740,23 +2760,19 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O35" s="6" t="n">
@@ -2764,25 +2780,25 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46109</v>
+        <v>46107</v>
       </c>
       <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>12</v>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2799,15 +2815,19 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr"/>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="M36" s="6" t="inlineStr"/>
       <c r="N36" s="6" t="inlineStr">
         <is>
@@ -2819,14 +2839,14 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46112</v>
+        <v>46107</v>
       </c>
       <c r="B37" s="5" t="inlineStr"/>
       <c r="C37" s="5" t="inlineStr"/>
@@ -2859,12 +2879,12 @@
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
@@ -2878,27 +2898,25 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46107</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>16</v>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -2906,7 +2924,7 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
@@ -2915,23 +2933,23 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr"/>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -2939,27 +2957,27 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>12</v>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
@@ -2976,16 +2994,24 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2996,27 +3022,27 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>16</v>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>34</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
@@ -3033,20 +3059,24 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr"/>
+          <t>hot-model, running, women, exclusive</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3057,27 +3087,27 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>16</v>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -3094,20 +3124,24 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3118,17 +3152,17 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
@@ -3160,10 +3194,14 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr"/>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M42" s="6" t="inlineStr"/>
       <c r="N42" s="6" t="inlineStr">
         <is>
@@ -3175,27 +3213,27 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>12</v>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3217,12 +3255,12 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr"/>
@@ -3236,27 +3274,27 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>7</v>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3273,17 +3311,17 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr"/>
@@ -3297,17 +3335,17 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
@@ -3334,17 +3372,17 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
@@ -3358,17 +3396,17 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
@@ -3395,19 +3433,15 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr"/>
       <c r="N46" s="6" t="inlineStr">
         <is>
@@ -3419,25 +3453,27 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr"/>
+        <v>46107</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="n">
-        <v>24</v>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3445,7 +3481,7 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
@@ -3454,34 +3490,1379 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+        </is>
+      </c>
+      <c r="Q47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="Q48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/order/search</t>
+        </is>
+      </c>
+      <c r="Q49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+        </is>
+      </c>
+      <c r="Q50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+        </is>
+      </c>
+      <c r="Q51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>#main</t>
+        </is>
+      </c>
+      <c r="Q52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/help/store-pickup</t>
+        </is>
+      </c>
+      <c r="Q53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="Q54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr"/>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>Converse x NOAH Chuck 70</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="O47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" s="12" t="inlineStr">
+      <c r="O55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr"/>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr"/>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+        </is>
+      </c>
+      <c r="Q57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr"/>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+        </is>
+      </c>
+      <c r="L58" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+        </is>
+      </c>
+      <c r="Q58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+        </is>
+      </c>
+      <c r="Q60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L62" s="12" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+        </is>
+      </c>
+      <c r="Q62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="6" t="inlineStr"/>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr"/>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+        </is>
+      </c>
+      <c r="Q63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L64" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr"/>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="L66" s="12" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr"/>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+        </is>
+      </c>
+      <c r="Q66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr"/>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L68" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr"/>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="6" t="inlineStr"/>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr"/>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="L70" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr"/>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
-      <c r="Q47" s="12" t="inlineStr"/>
+      <c r="Q70" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3498,7 +4879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3556,22 +4937,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3579,7 +4960,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-24T07:39:40Z</t>
+          <t>2026-03-24T19:37:58Z</t>
         </is>
       </c>
     </row>
@@ -3591,7 +4972,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3609,7 +4990,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-24T07:39:40Z</t>
+          <t>2026-03-24T19:37:58Z</t>
         </is>
       </c>
     </row>
@@ -3621,7 +5002,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3639,7 +5020,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-24T07:39:40Z</t>
+          <t>2026-03-24T19:37:58Z</t>
         </is>
       </c>
     </row>
@@ -3651,7 +5032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3669,7 +5050,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-24T07:39:40Z</t>
+          <t>2026-03-24T19:37:58Z</t>
         </is>
       </c>
     </row>
@@ -3681,7 +5062,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3691,7 +5072,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -3699,7 +5080,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-24T07:39:40Z</t>
+          <t>2026-03-24T19:37:58Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +5092,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3721,7 +5102,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -3729,7 +5110,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-24T07:39:40Z</t>
+          <t>2026-03-24T19:37:58Z</t>
         </is>
       </c>
     </row>
@@ -3741,7 +5122,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3751,7 +5132,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -3759,7 +5140,487 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-24T07:39:40Z</t>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Converse x NOAH Chuck 70</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-24T19:37:58Z</t>
         </is>
       </c>
     </row>
@@ -3774,7 +5635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5586,7 +7447,7 @@
         <v>46107</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5605,28 +7466,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -5634,16 +7499,16 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="Q28" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>
@@ -5652,7 +7517,7 @@
         <v>46107</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5671,28 +7536,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -5700,16 +7569,16 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R29" t="inlineStr"/>
     </row>
@@ -5718,11 +7587,11 @@
         <v>46107</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5737,28 +7606,28 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5766,29 +7635,29 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5803,28 +7672,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5832,25 +7701,25 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q31" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5869,12 +7738,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5885,12 +7754,12 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -5898,29 +7767,29 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q32" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46109</v>
+        <v>46107</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5935,28 +7804,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -5964,29 +7829,29 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46109</v>
+        <v>46107</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6001,15 +7866,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
@@ -6026,13 +7895,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q34" t="n">
         <v>50</v>
@@ -6041,7 +7910,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46112</v>
+        <v>46107</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -6068,12 +7937,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -6092,7 +7961,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -6107,14 +7976,14 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6129,28 +7998,28 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -6158,29 +8027,29 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q36" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B37" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6195,16 +8064,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6220,13 +8097,13 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q37" t="n">
         <v>59</v>
@@ -6235,14 +8112,14 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6257,20 +8134,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>hot-model, running, women, exclusive</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6286,13 +8167,13 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="Q38" t="n">
         <v>59</v>
@@ -6301,14 +8182,14 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B39" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6323,20 +8204,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6352,13 +8237,13 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q39" t="n">
         <v>59</v>
@@ -6367,10 +8252,10 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B40" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6394,10 +8279,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
@@ -6414,7 +8303,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -6429,14 +8318,14 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B41" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6456,12 +8345,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6480,13 +8369,13 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
         <v>59</v>
@@ -6495,14 +8384,14 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B42" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6517,17 +8406,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6546,13 +8435,13 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q42" t="n">
         <v>59</v>
@@ -6561,10 +8450,10 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B43" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6583,17 +8472,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6612,7 +8501,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6627,10 +8516,10 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B44" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6649,19 +8538,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
@@ -6678,7 +8563,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6693,14 +8578,14 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46115</v>
+        <v>46107</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6715,28 +8600,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -6744,18 +8625,1496 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>59</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B46" t="n">
+        <v>190</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>59</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B47" t="n">
+        <v>190</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/order/search</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>59</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B48" t="n">
+        <v>190</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>59</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B49" t="n">
+        <v>190</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>59</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B50" t="n">
+        <v>190</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>#main</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>59</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B51" t="n">
+        <v>190</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/help/store-pickup</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>59</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" t="n">
+        <v>190</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>59</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Converse x NOAH Chuck 70</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>50</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>50</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>50</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>50</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>50</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
         <v>24</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q58" t="n">
         <v>50</v>
       </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B59" t="n">
+        <v>150</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>59</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B60" t="n">
+        <v>150</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>59</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B61" t="n">
+        <v>150</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>59</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B62" t="n">
+        <v>150</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>59</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B63" t="n">
+        <v>150</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>59</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B64" t="n">
+        <v>150</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>59</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>150</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>59</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B66" t="n">
+        <v>150</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>59</v>
+      </c>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B67" t="n">
+        <v>130</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>59</v>
+      </c>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>50</v>
+      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6929,7 +10288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6948,7 +10307,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  44 releases</t>
+          <t>Next 35 Days  ·  67 releases</t>
         </is>
       </c>
     </row>
@@ -6966,7 +10325,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -7027,7 +10386,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$161</t>
+          <t>$172</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -7084,7 +10443,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -7092,7 +10451,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -7102,7 +10461,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -7127,7 +10486,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -7146,7 +10505,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -7158,15 +10517,15 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>████████████</t>
+          <t>█████████████</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>
@@ -7174,15 +10533,15 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B24" s="39" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>█████████</t>
+          <t>████████████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -7190,11 +10549,11 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="38" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B25" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
@@ -7206,15 +10565,15 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B26" s="39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D26" s="21" t="n"/>
@@ -7222,11 +10581,11 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B27" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
@@ -7234,6 +10593,22 @@
         </is>
       </c>
       <c r="D27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -855,10 +855,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
@@ -920,10 +920,10 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
@@ -985,20 +985,20 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>28</v>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
@@ -1039,17 +1039,17 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
@@ -1100,17 +1100,17 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr"/>
@@ -1161,17 +1161,17 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
@@ -1203,14 +1203,10 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
@@ -1222,27 +1218,25 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>165</v>
-      </c>
+        <v>46107</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>7</v>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1250,7 +1244,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1259,19 +1253,23 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr"/>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1279,18 +1277,16 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>165</v>
-      </c>
+        <v>46107</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
@@ -1299,7 +1295,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1307,7 +1303,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1321,22 +1317,18 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>exclusive</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1344,18 +1336,16 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>165</v>
-      </c>
+        <v>46107</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="7" t="inlineStr">
@@ -1364,7 +1354,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1372,7 +1362,7 @@
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -1386,22 +1376,18 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, women, exclusive</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1409,17 +1395,17 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
@@ -1451,12 +1437,12 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -1474,27 +1460,27 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>12</v>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>34</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1516,11 +1502,19 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, women, exclusive</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1531,17 +1525,17 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1551,7 +1545,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1573,15 +1567,19 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1592,17 +1590,17 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
@@ -1634,7 +1632,7 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
@@ -1653,27 +1651,27 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>12</v>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1695,12 +1693,12 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
@@ -1714,17 +1712,17 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1756,7 +1754,7 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
@@ -1775,27 +1773,27 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>24</v>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1812,17 +1810,17 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
@@ -1836,17 +1834,17 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1878,14 +1876,10 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -1897,17 +1891,17 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1917,7 +1911,7 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1934,12 +1928,12 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr"/>
@@ -1954,17 +1948,17 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1996,7 +1990,7 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr"/>
@@ -2011,17 +2005,17 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
@@ -2053,7 +2047,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2068,17 +2062,17 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
@@ -2110,7 +2104,7 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr"/>
@@ -2125,17 +2119,17 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
@@ -2167,7 +2161,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
@@ -2182,17 +2176,17 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
@@ -2224,7 +2218,7 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr"/>
@@ -2239,17 +2233,17 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
@@ -2281,7 +2275,7 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr"/>
@@ -2296,17 +2290,17 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
@@ -2338,7 +2332,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr"/>
@@ -2353,18 +2347,16 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>165</v>
-      </c>
+        <v>46108</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr">
@@ -2373,7 +2365,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2381,7 +2373,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2390,19 +2382,23 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr"/>
+          <t>Converse x Noah Chuck 70</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
       <c r="M29" s="6" t="inlineStr"/>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2410,18 +2406,16 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>190</v>
-      </c>
+        <v>46108</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
@@ -2430,7 +2424,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2438,7 +2432,7 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2447,27 +2441,23 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr"/>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O30" s="6" t="n">
@@ -2475,27 +2465,25 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>190</v>
-      </c>
+        <v>46108</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>26</v>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2503,7 +2491,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2512,27 +2500,23 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O31" s="6" t="n">
@@ -2540,27 +2524,25 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>190</v>
-      </c>
+        <v>46109</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>16</v>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2568,7 +2550,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2582,18 +2564,18 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O32" s="6" t="n">
@@ -2601,18 +2583,16 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>190</v>
-      </c>
+        <v>46109</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="13" t="inlineStr">
@@ -2621,7 +2601,7 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2629,7 +2609,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2643,18 +2623,14 @@
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -2662,27 +2638,25 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>190</v>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>7</v>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2690,7 +2664,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2699,23 +2673,23 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O34" s="6" t="n">
@@ -2723,17 +2697,17 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
@@ -2743,7 +2717,7 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2760,15 +2734,19 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr"/>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr">
         <is>
@@ -2780,25 +2758,27 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>24</v>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2806,7 +2786,7 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
@@ -2815,23 +2795,19 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr"/>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
@@ -2839,25 +2815,27 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>24</v>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2865,7 +2843,7 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
@@ -2874,23 +2852,23 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
@@ -2898,25 +2876,27 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>24</v>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -2924,7 +2904,7 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
@@ -2933,23 +2913,23 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr"/>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -2957,27 +2937,27 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>22</v>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
@@ -2999,19 +2979,11 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr"/>
       <c r="N39" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3022,27 +2994,27 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>34</v>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
@@ -3064,19 +3036,15 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, women, exclusive</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr"/>
       <c r="N40" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3087,27 +3055,27 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>22</v>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -3124,24 +3092,20 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr"/>
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3152,17 +3116,17 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
@@ -3172,7 +3136,7 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -3189,17 +3153,17 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr"/>
@@ -3213,27 +3177,27 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>24</v>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3250,17 +3214,17 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr"/>
@@ -3274,18 +3238,16 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>190</v>
-      </c>
+        <v>46115</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr"/>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
@@ -3302,7 +3264,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3316,18 +3278,18 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr"/>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O44" s="6" t="n">
@@ -3335,1534 +3297,10 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
-        </is>
-      </c>
-      <c r="Q45" s="12" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr"/>
-      <c r="M46" s="6" t="inlineStr"/>
-      <c r="N46" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
-        </is>
-      </c>
-      <c r="Q46" s="12" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr"/>
-      <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
-        </is>
-      </c>
-      <c r="Q47" s="12" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C48" s="5" t="inlineStr"/>
-      <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr"/>
-      <c r="M48" s="6" t="inlineStr"/>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
-        </is>
-      </c>
-      <c r="Q48" s="12" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C49" s="5" t="inlineStr"/>
-      <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr"/>
-      <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/order/search</t>
-        </is>
-      </c>
-      <c r="Q49" s="12" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr"/>
-      <c r="M50" s="6" t="inlineStr"/>
-      <c r="N50" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
-        </is>
-      </c>
-      <c r="Q50" s="12" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="6" t="inlineStr"/>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr"/>
-      <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
-        </is>
-      </c>
-      <c r="Q51" s="12" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="6" t="inlineStr"/>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr"/>
-      <c r="M52" s="6" t="inlineStr"/>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" s="12" t="inlineStr">
-        <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="Q52" s="12" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="6" t="inlineStr"/>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr"/>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P53" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
-        </is>
-      </c>
-      <c r="Q53" s="12" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="6" t="inlineStr"/>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr"/>
-      <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar</t>
-        </is>
-      </c>
-      <c r="Q54" s="12" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr"/>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="6" t="inlineStr"/>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="K55" s="12" t="inlineStr">
-        <is>
-          <t>Converse x NOAH Chuck 70</t>
-        </is>
-      </c>
-      <c r="L55" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
-      <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
-        </is>
-      </c>
-      <c r="Q55" s="12" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr"/>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="6" t="inlineStr"/>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
-        </is>
-      </c>
-      <c r="L56" s="12" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
-      <c r="M56" s="6" t="inlineStr"/>
-      <c r="N56" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
-        </is>
-      </c>
-      <c r="Q56" s="12" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr"/>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="6" t="inlineStr"/>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="L57" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
-        </is>
-      </c>
-      <c r="Q57" s="12" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr"/>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="6" t="inlineStr"/>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
-        </is>
-      </c>
-      <c r="L58" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="M58" s="6" t="inlineStr"/>
-      <c r="N58" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
-        </is>
-      </c>
-      <c r="Q58" s="12" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="6" t="inlineStr"/>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="L59" s="12" t="inlineStr"/>
-      <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O59" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
-        </is>
-      </c>
-      <c r="Q59" s="12" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="6" t="inlineStr"/>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
-        </is>
-      </c>
-      <c r="L60" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
-      <c r="M60" s="6" t="inlineStr"/>
-      <c r="N60" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
-        </is>
-      </c>
-      <c r="Q60" s="12" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="6" t="inlineStr"/>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K61" s="12" t="inlineStr">
-        <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="L61" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
-        </is>
-      </c>
-      <c r="Q61" s="12" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="6" t="inlineStr"/>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K62" s="12" t="inlineStr">
-        <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="L62" s="12" t="inlineStr"/>
-      <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
-        </is>
-      </c>
-      <c r="Q62" s="12" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C63" s="5" t="inlineStr"/>
-      <c r="D63" s="6" t="inlineStr"/>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr">
-        <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="L63" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
-        </is>
-      </c>
-      <c r="Q63" s="12" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="6" t="inlineStr"/>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K64" s="12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L64" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O64" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="Q64" s="12" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C65" s="5" t="inlineStr"/>
-      <c r="D65" s="6" t="inlineStr"/>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K65" s="12" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L65" s="12" t="inlineStr"/>
-      <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="Q65" s="12" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C66" s="5" t="inlineStr"/>
-      <c r="D66" s="6" t="inlineStr"/>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K66" s="12" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
-        </is>
-      </c>
-      <c r="L66" s="12" t="inlineStr">
-        <is>
-          <t>basketball, kids</t>
-        </is>
-      </c>
-      <c r="M66" s="6" t="inlineStr"/>
-      <c r="N66" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
-        </is>
-      </c>
-      <c r="Q66" s="12" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C67" s="5" t="inlineStr"/>
-      <c r="D67" s="6" t="inlineStr"/>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K67" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L67" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="Q67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B68" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="6" t="inlineStr"/>
-      <c r="E68" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K68" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L68" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="Q68" s="12" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C69" s="5" t="inlineStr"/>
-      <c r="D69" s="6" t="inlineStr"/>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K69" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L69" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="Q69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr"/>
-      <c r="C70" s="5" t="inlineStr"/>
-      <c r="D70" s="6" t="inlineStr"/>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K70" s="12" t="inlineStr">
-        <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="L70" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O70" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="Q70" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4879,7 +3317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4937,12 +3375,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4960,19 +3398,19 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4990,19 +3428,19 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5020,19 +3458,19 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5050,19 +3488,19 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5080,19 +3518,19 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5110,19 +3548,19 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5132,7 +3570,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -5140,19 +3578,19 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5162,7 +3600,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -5170,29 +3608,29 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -5200,29 +3638,29 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -5230,19 +3668,19 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5252,7 +3690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -5260,19 +3698,19 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5282,7 +3720,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -5290,29 +3728,29 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -5320,29 +3758,29 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -5350,29 +3788,29 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -5380,29 +3818,29 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -5410,29 +3848,29 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -5440,29 +3878,29 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -5470,29 +3908,29 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -5500,29 +3938,29 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -5530,29 +3968,29 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -5560,19 +3998,19 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5582,7 +4020,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -5590,29 +4028,29 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Converse x NOAH Chuck 70</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -5620,7 +4058,97 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-24T19:37:58Z</t>
+          <t>2026-03-25T07:38:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-03-25T07:38:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-03-25T07:38:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-03-25T07:38:35Z</t>
         </is>
       </c>
     </row>
@@ -5635,7 +4163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5752,10 +4280,10 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B2" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5822,10 +4350,10 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B3" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5892,14 +4420,14 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B4" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5919,12 +4447,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -5943,13 +4471,13 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Q4" t="n">
         <v>59</v>
@@ -5958,10 +4486,10 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5985,7 +4513,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6009,7 +4537,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -6024,10 +4552,10 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B6" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6046,17 +4574,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -6075,13 +4603,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>59</v>
@@ -6090,10 +4618,10 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6117,14 +4645,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -6141,7 +4665,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -6156,14 +4680,14 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6178,24 +4702,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -6203,25 +4731,25 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6245,27 +4773,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>exclusive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -6273,25 +4797,25 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6315,27 +4839,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>hot-model, running, women, exclusive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -6343,25 +4863,25 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B11" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6385,12 +4905,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -6413,7 +4933,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -6428,14 +4948,14 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B12" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6455,11 +4975,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hot-model, running, women, exclusive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6475,13 +5003,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -6490,10 +5018,10 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B13" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6517,15 +5045,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6541,13 +5073,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -6556,10 +5088,10 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B14" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6583,7 +5115,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6607,7 +5139,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -6622,14 +5154,14 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B15" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6649,12 +5181,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -6673,13 +5205,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -6688,10 +5220,10 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B16" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6715,7 +5247,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6739,7 +5271,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -6754,14 +5286,14 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B17" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6776,17 +5308,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -6805,13 +5337,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -6820,10 +5352,10 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B18" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6847,14 +5379,10 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -6871,7 +5399,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -6886,10 +5414,10 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B19" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6908,12 +5436,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -6933,13 +5461,13 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>59</v>
@@ -6948,10 +5476,10 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B20" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6975,7 +5503,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -6995,7 +5523,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -7010,10 +5538,10 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B21" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7037,7 +5565,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -7057,7 +5585,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -7072,10 +5600,10 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B22" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7099,7 +5627,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -7119,7 +5647,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -7134,10 +5662,10 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B23" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7161,7 +5689,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -7181,7 +5709,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -7196,10 +5724,10 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B24" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7223,7 +5751,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -7243,7 +5771,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -7258,10 +5786,10 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B25" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7285,7 +5813,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -7305,7 +5833,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -7320,10 +5848,10 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B26" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7347,7 +5875,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -7367,7 +5895,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -7382,10 +5910,10 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="B27" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7404,24 +5932,28 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Converse x Noah Chuck 70</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -7429,25 +5961,25 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B28" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7466,32 +5998,28 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -7499,29 +6027,29 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B29" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -7536,32 +6064,28 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -7569,29 +6093,29 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="B30" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -7611,23 +6135,23 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -7635,25 +6159,25 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="B31" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7677,23 +6201,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -7701,29 +6221,29 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B32" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -7738,28 +6258,28 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -7767,25 +6287,25 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q32" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B33" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7804,15 +6324,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
@@ -7829,13 +6353,13 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q33" t="n">
         <v>59</v>
@@ -7844,14 +6368,14 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7866,28 +6390,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -7895,29 +6415,29 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q34" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7932,28 +6452,28 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -7961,29 +6481,29 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q35" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7998,28 +6518,28 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -8027,29 +6547,29 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B37" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8069,19 +6589,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -8097,13 +6609,13 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q37" t="n">
         <v>59</v>
@@ -8112,14 +6624,14 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B38" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8139,19 +6651,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>hot-model, running, women, exclusive</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -8167,13 +6675,13 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="Q38" t="n">
         <v>59</v>
@@ -8182,14 +6690,14 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B39" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8204,24 +6712,20 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -8237,13 +6741,13 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Q39" t="n">
         <v>59</v>
@@ -8252,10 +6756,10 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B40" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -8274,17 +6778,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -8303,13 +6807,13 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="n">
         <v>59</v>
@@ -8318,14 +6822,14 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B41" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8340,17 +6844,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -8369,13 +6873,13 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q41" t="n">
         <v>59</v>
@@ -8384,10 +6888,10 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="B42" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -8411,23 +6915,23 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -8435,7 +6939,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -8444,1677 +6948,9 @@
         <v>24</v>
       </c>
       <c r="Q42" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B43" t="n">
-        <v>190</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>59</v>
-      </c>
-      <c r="R43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B44" t="n">
-        <v>190</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>59</v>
-      </c>
-      <c r="R44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B45" t="n">
-        <v>190</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>59</v>
-      </c>
-      <c r="R45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B46" t="n">
-        <v>190</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>59</v>
-      </c>
-      <c r="R46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B47" t="n">
-        <v>190</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/order/search</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>59</v>
-      </c>
-      <c r="R47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B48" t="n">
-        <v>190</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>59</v>
-      </c>
-      <c r="R48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B49" t="n">
-        <v>190</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>59</v>
-      </c>
-      <c r="R49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B50" t="n">
-        <v>190</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>59</v>
-      </c>
-      <c r="R50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B51" t="n">
-        <v>190</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>59</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B52" t="n">
-        <v>190</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>59</v>
-      </c>
-      <c r="R52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Converse x NOAH Chuck 70</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>50</v>
-      </c>
-      <c r="R53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>50</v>
-      </c>
-      <c r="R54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>50</v>
-      </c>
-      <c r="R55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>50</v>
-      </c>
-      <c r="R56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>50</v>
-      </c>
-      <c r="R57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>50</v>
-      </c>
-      <c r="R58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B59" t="n">
-        <v>150</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>59</v>
-      </c>
-      <c r="R59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B60" t="n">
-        <v>150</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>59</v>
-      </c>
-      <c r="R60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B61" t="n">
-        <v>150</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>59</v>
-      </c>
-      <c r="R61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B62" t="n">
-        <v>150</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>59</v>
-      </c>
-      <c r="R62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B63" t="n">
-        <v>150</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>59</v>
-      </c>
-      <c r="R63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B64" t="n">
-        <v>150</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>basketball, kids</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>59</v>
-      </c>
-      <c r="R64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B65" t="n">
-        <v>150</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>59</v>
-      </c>
-      <c r="R65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B66" t="n">
-        <v>150</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>59</v>
-      </c>
-      <c r="R66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B67" t="n">
-        <v>130</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>59</v>
-      </c>
-      <c r="R67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>50</v>
-      </c>
-      <c r="R68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10307,7 +7143,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  67 releases</t>
+          <t>Next 35 Days  ·  41 releases</t>
         </is>
       </c>
     </row>
@@ -10325,7 +7161,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -10386,7 +7222,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$172</t>
+          <t>$178</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -10443,7 +7279,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -10451,7 +7287,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -10461,7 +7297,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -10486,7 +7322,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -10505,7 +7341,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -10517,11 +7353,11 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
@@ -10533,15 +7369,15 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B24" s="39" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>████████████</t>
+          <t>███████████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -10549,15 +7385,15 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="38" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B25" s="39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>███</t>
+          <t>████</t>
         </is>
       </c>
       <c r="D25" s="21" t="n"/>
@@ -10565,11 +7401,11 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B26" s="39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
@@ -10581,15 +7417,15 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B27" s="39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D27" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, women, exclusive</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
+          <t>hot-model, running, women, exclusive</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -1604,13 +1604,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>12</v>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1632,15 +1632,19 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1665,13 +1669,13 @@
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>24</v>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1693,12 +1697,12 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1754,7 +1758,7 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
@@ -1773,7 +1777,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1787,13 +1791,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>7</v>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1810,17 +1814,17 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
@@ -1834,7 +1838,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1876,10 +1880,14 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr"/>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -1891,7 +1899,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1911,7 +1919,7 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1928,12 +1936,12 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr"/>
@@ -1948,7 +1956,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1990,7 +1998,7 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr"/>
@@ -2005,7 +2013,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2047,7 +2055,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2062,7 +2070,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2104,7 +2112,7 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr"/>
@@ -2119,7 +2127,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2161,7 +2169,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
@@ -2176,7 +2184,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2218,7 +2226,7 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr"/>
@@ -2233,7 +2241,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2275,7 +2283,7 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr"/>
@@ -2290,7 +2298,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2332,7 +2340,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr"/>
@@ -2347,16 +2355,18 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr"/>
+        <v>46107</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>190</v>
+      </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr">
@@ -2365,7 +2375,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2373,7 +2383,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2382,23 +2392,19 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Converse x Noah Chuck 70</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr"/>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2406,7 +2412,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2418,13 +2424,13 @@
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>22</v>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2441,17 +2447,17 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+          <t>Converse x Noah Chuck 70</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2465,7 +2471,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2477,13 +2483,13 @@
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>12</v>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2505,12 +2511,12 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
@@ -2524,25 +2530,25 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>28</v>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2559,17 +2565,17 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
@@ -2583,7 +2589,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -2595,13 +2601,13 @@
       <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>12</v>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2623,10 +2629,14 @@
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
@@ -2638,25 +2648,25 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46112</v>
+        <v>46109</v>
       </c>
       <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>24</v>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2673,19 +2683,15 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
@@ -2697,27 +2703,25 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>16</v>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2725,7 +2729,7 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
@@ -2734,23 +2738,23 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr"/>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O35" s="6" t="n">
@@ -2758,7 +2762,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -2778,7 +2782,7 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2800,10 +2804,14 @@
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr"/>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M36" s="6" t="inlineStr"/>
       <c r="N36" s="6" t="inlineStr">
         <is>
@@ -2815,7 +2823,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -2835,7 +2843,7 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2857,14 +2865,10 @@
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
@@ -2876,7 +2880,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -2918,12 +2922,12 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr"/>
@@ -2937,7 +2941,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -2957,7 +2961,7 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
@@ -2974,15 +2978,19 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="M39" s="6" t="inlineStr"/>
       <c r="N39" s="6" t="inlineStr">
         <is>
@@ -2994,7 +3002,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -3036,7 +3044,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
@@ -3051,7 +3059,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -3093,7 +3101,7 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr"/>
@@ -3108,7 +3116,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
@@ -3150,7 +3158,7 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr"/>
@@ -3165,7 +3173,7 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
@@ -3207,14 +3215,10 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>basketball, kids</t>
-        </is>
-      </c>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr"/>
       <c r="N43" s="6" t="inlineStr">
         <is>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
@@ -3268,12 +3272,12 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>basketball, kids</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr"/>
@@ -3287,7 +3291,7 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
@@ -3307,7 +3311,7 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3324,17 +3328,17 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
@@ -3390,7 +3394,7 @@
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
@@ -3409,7 +3413,7 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
@@ -3419,7 +3423,7 @@
         <v>46113</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
@@ -3451,7 +3455,7 @@
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
@@ -3477,18 +3481,20 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>24</v>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3496,7 +3502,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3505,34 +3511,93 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="O48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P48" s="12" t="inlineStr">
+      <c r="O49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
-      <c r="Q48" s="12" t="inlineStr"/>
+      <c r="Q49" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3549,13 +3614,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="57" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -3612,7 +3677,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3622,7 +3687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
+          <t>App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3630,97 +3695,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-25T18:38:47Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-25T18:38:47Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-25T18:38:47Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-25T18:38:47Z</t>
+          <t>2026-03-26T07:46:21Z</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4477,12 +4452,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4505,13 +4480,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -4547,12 +4522,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>hot-model, running, women, exclusive</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4575,13 +4550,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -4617,12 +4592,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
+          <t>hot-model, running, women, exclusive</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4645,13 +4620,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -4667,7 +4642,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4687,15 +4662,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4711,13 +4690,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -4733,7 +4712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4753,12 +4732,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>hot-model, running, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -4777,13 +4756,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7232400.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -4819,7 +4798,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4843,7 +4822,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -4865,7 +4844,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4880,17 +4859,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -4909,13 +4888,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -4951,10 +4930,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -4971,7 +4954,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -5008,12 +4991,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -5033,13 +5016,13 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
         <v>59</v>
@@ -5075,7 +5058,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -5095,7 +5078,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -5137,7 +5120,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -5157,7 +5140,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -5199,7 +5182,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -5219,7 +5202,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5261,7 +5244,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -5281,7 +5264,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -5323,7 +5306,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -5343,7 +5326,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -5385,7 +5368,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -5405,7 +5388,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -5447,7 +5430,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -5467,7 +5450,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -5482,10 +5465,10 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5504,28 +5487,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Converse x Noah Chuck 70</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5533,16 +5512,16 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
@@ -5555,7 +5534,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5570,17 +5549,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+          <t>Converse x Noah Chuck 70</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -5599,13 +5578,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.nike.com/launch/t/converse-noah-chuck-70</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
         <v>50</v>
@@ -5621,7 +5600,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5641,12 +5620,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -5665,13 +5644,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q29" t="n">
         <v>50</v>
@@ -5680,14 +5659,14 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5702,17 +5681,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -5731,13 +5710,13 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Q30" t="n">
         <v>50</v>
@@ -5753,7 +5732,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5773,10 +5752,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
@@ -5793,13 +5776,13 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q31" t="n">
         <v>50</v>
@@ -5808,14 +5791,14 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46112</v>
+        <v>46109</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5830,19 +5813,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -5859,13 +5838,13 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q32" t="n">
         <v>50</v>
@@ -5874,14 +5853,14 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="B33" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5896,28 +5875,28 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -5925,16 +5904,16 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q33" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R33" t="inlineStr"/>
     </row>
@@ -5967,10 +5946,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
@@ -5987,13 +5970,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q34" t="n">
         <v>59</v>
@@ -6029,14 +6012,10 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
@@ -6053,13 +6032,13 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q35" t="n">
         <v>59</v>
@@ -6095,12 +6074,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -6119,7 +6098,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -6156,15 +6135,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
@@ -6181,13 +6164,13 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q37" t="n">
         <v>59</v>
@@ -6223,7 +6206,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6243,7 +6226,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -6285,7 +6268,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -6305,7 +6288,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -6347,7 +6330,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -6367,7 +6350,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -6409,14 +6392,10 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>basketball, kids</t>
-        </is>
-      </c>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
@@ -6433,7 +6412,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -6475,12 +6454,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>basketball, kids</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6499,7 +6478,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6536,17 +6515,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6565,13 +6544,13 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
         <v>59</v>
@@ -6607,7 +6586,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6631,7 +6610,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6649,7 +6628,7 @@
         <v>46113</v>
       </c>
       <c r="B45" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6673,7 +6652,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6712,14 +6691,14 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6734,28 +6713,28 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -6763,18 +6742,84 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>59</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
         <v>24</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q47" t="n">
         <v>50</v>
       </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6967,7 +7012,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  45 releases</t>
+          <t>Next 35 Days  ·  46 releases</t>
         </is>
       </c>
     </row>
@@ -6985,7 +7030,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -7103,7 +7148,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -7111,7 +7156,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -7146,7 +7191,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -7165,7 +7210,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -7185,7 +7230,7 @@
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>███████████</t>
+          <t>██████████</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -2354,16 +2354,18 @@
       <c r="A29" s="4" t="n">
         <v>46109</v>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>12</v>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>38</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2371,7 +2373,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2385,14 +2387,22 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr"/>
-      <c r="M29" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2400,16 +2410,18 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr"/>
+        <v>46109</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
@@ -2418,7 +2430,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2426,7 +2438,7 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2435,23 +2447,27 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O30" s="6" t="n">
@@ -2459,18 +2475,16 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46109</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="13" t="inlineStr">
@@ -2479,7 +2493,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2487,7 +2501,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2501,18 +2515,14 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O31" s="6" t="n">
@@ -2520,17 +2530,17 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
@@ -2540,7 +2550,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2562,10 +2572,14 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="L32" s="12" t="inlineStr"/>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
@@ -2577,17 +2591,17 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
@@ -2619,7 +2633,7 @@
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
@@ -2638,17 +2652,17 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
@@ -2658,7 +2672,7 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2675,19 +2689,15 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
@@ -2699,17 +2709,17 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
@@ -2719,7 +2729,7 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2736,12 +2746,12 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr"/>
@@ -2756,17 +2766,17 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -2776,7 +2786,7 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2793,12 +2803,12 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr"/>
@@ -2813,17 +2823,17 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
@@ -2833,7 +2843,7 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2850,12 +2860,12 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr"/>
@@ -2870,17 +2880,17 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="6" t="inlineStr"/>
@@ -2890,7 +2900,7 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -2907,12 +2917,12 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr"/>
@@ -2927,17 +2937,17 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
@@ -2947,7 +2957,7 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
@@ -2964,19 +2974,15 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>basketball, kids</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr"/>
       <c r="N39" s="6" t="inlineStr">
         <is>
@@ -2988,17 +2994,17 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
@@ -3008,7 +3014,7 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
@@ -3025,19 +3031,15 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
-        </is>
-      </c>
-      <c r="L40" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr"/>
       <c r="N40" s="6" t="inlineStr">
         <is>
@@ -3049,16 +3051,18 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
+        <v>46109</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
       <c r="E41" s="13" t="inlineStr">
@@ -3067,7 +3071,7 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -3075,7 +3079,7 @@
         </is>
       </c>
       <c r="H41" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
@@ -3084,23 +3088,19 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr"/>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O41" s="6" t="n">
@@ -3108,27 +3108,25 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>7</v>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -3136,7 +3134,7 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -3145,23 +3143,23 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr"/>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O42" s="6" t="n">
@@ -3169,7 +3167,7 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
@@ -3179,7 +3177,7 @@
         <v>46113</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
@@ -3189,7 +3187,7 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3206,17 +3204,17 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr"/>
@@ -3230,7 +3228,7 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
@@ -3240,7 +3238,7 @@
         <v>46113</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
@@ -3250,7 +3248,7 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3267,17 +3265,17 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr"/>
@@ -3291,25 +3289,27 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>155</v>
+      </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>24</v>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
@@ -3326,34 +3326,986 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr"/>
       <c r="N45" s="6" t="inlineStr">
         <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+        </is>
+      </c>
+      <c r="Q45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+        </is>
+      </c>
+      <c r="Q46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr"/>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
+        </is>
+      </c>
+      <c r="Q48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
+        </is>
+      </c>
+      <c r="Q49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
+        </is>
+      </c>
+      <c r="Q50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+        </is>
+      </c>
+      <c r="Q51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+        </is>
+      </c>
+      <c r="Q52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+        </is>
+      </c>
+      <c r="Q54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr"/>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
-      <c r="O45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" s="12" t="inlineStr">
+      <c r="O57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+        </is>
+      </c>
+      <c r="Q57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L58" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
         <is>
           <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
-      <c r="Q45" s="12" t="inlineStr"/>
+      <c r="Q61" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3370,10 +4322,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -3428,22 +4380,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3451,29 +4403,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -3481,29 +4433,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -3511,29 +4463,29 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -3541,29 +4493,29 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -3571,29 +4523,29 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -3601,29 +4553,29 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -3631,29 +4583,29 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -3661,29 +4613,29 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -3691,29 +4643,29 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -3721,29 +4673,29 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -3751,29 +4703,29 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -3781,29 +4733,29 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -3811,19 +4763,19 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3833,7 +4785,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS PRE-SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -3841,19 +4793,19 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3863,7 +4815,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -3871,19 +4823,19 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3893,7 +4845,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -3901,367 +4853,427 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>RETAIL_CHANGED</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-27T07:46:25Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>App Entry Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-27T07:46:25Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>App Entry Nike Grade School Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-27T07:46:25Z</t>
+          <t>2026-03-27T18:38:30Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +5288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6026,11 +7038,11 @@
         <v>46109</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6050,19 +7062,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -6070,25 +7090,25 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46112</v>
+        <v>46109</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6107,28 +7127,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -6136,25 +7160,25 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q28" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B29" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6178,23 +7202,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -6202,25 +7222,25 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B30" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6244,10 +7264,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
@@ -6264,13 +7288,13 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q30" t="n">
         <v>59</v>
@@ -6279,10 +7303,10 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B31" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6306,7 +7330,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6330,7 +7354,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -6345,10 +7369,10 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B32" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6367,19 +7391,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -6396,13 +7416,13 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>59</v>
@@ -6411,10 +7431,10 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B33" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6433,12 +7453,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -6458,13 +7478,13 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>59</v>
@@ -6473,10 +7493,10 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B34" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6495,12 +7515,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -6520,13 +7540,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
         <v>59</v>
@@ -6535,10 +7555,10 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B35" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6557,12 +7577,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -6582,13 +7602,13 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
         <v>59</v>
@@ -6597,10 +7617,10 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B36" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -6619,12 +7639,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6644,13 +7664,13 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
         <v>59</v>
@@ -6659,10 +7679,10 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B37" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6681,19 +7701,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>basketball, kids</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
@@ -6710,13 +7726,13 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
         <v>59</v>
@@ -6725,10 +7741,10 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B38" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -6747,19 +7763,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
@@ -6776,13 +7788,13 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
         <v>59</v>
@@ -6791,10 +7803,10 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6813,28 +7825,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -6842,29 +7850,29 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="B40" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6879,28 +7887,28 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6908,16 +7916,16 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q40" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R40" t="inlineStr"/>
     </row>
@@ -6926,7 +7934,7 @@
         <v>46113</v>
       </c>
       <c r="B41" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6945,17 +7953,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6974,13 +7982,13 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q41" t="n">
         <v>59</v>
@@ -6992,7 +8000,7 @@
         <v>46113</v>
       </c>
       <c r="B42" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7011,17 +8019,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -7040,13 +8048,13 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q42" t="n">
         <v>59</v>
@@ -7055,14 +8063,14 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7077,28 +8085,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -7106,18 +8110,1058 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>59</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B44" t="n">
+        <v>155</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>59</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B45" t="n">
+        <v>155</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>59</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B46" t="n">
+        <v>155</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>59</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B47" t="n">
+        <v>155</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>59</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B48" t="n">
+        <v>155</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>59</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B49" t="n">
+        <v>150</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>59</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B50" t="n">
+        <v>150</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>59</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B51" t="n">
+        <v>155</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>59</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B52" t="n">
+        <v>155</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>59</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B53" t="n">
+        <v>155</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>59</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B54" t="n">
+        <v>155</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>59</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>50</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B56" t="n">
+        <v>155</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>59</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B57" t="n">
+        <v>155</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>59</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B58" t="n">
+        <v>130</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>59</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
         <v>24</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q59" t="n">
         <v>50</v>
       </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7310,7 +9354,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  42 releases</t>
+          <t>Next 35 Days  ·  58 releases</t>
         </is>
       </c>
     </row>
@@ -7328,7 +9372,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -7389,7 +9433,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$205</t>
+          <t>$204</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -7446,7 +9490,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -7454,7 +9498,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -7464,7 +9508,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -7489,7 +9533,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -7508,7 +9552,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -7520,15 +9564,15 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>████████████</t>
+          <t>█████████████████</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>
@@ -7536,15 +9580,15 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B24" s="39" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>██████████</t>
+          <t>████████████████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -7560,7 +9604,7 @@
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>████</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D25" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -328,9 +328,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -730,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -744,7 +741,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="11" max="11"/>
-    <col width="33" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -855,11 +852,9 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
@@ -868,7 +863,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -876,7 +871,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -885,27 +880,23 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr"/>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -913,17 +904,17 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
@@ -955,19 +946,15 @@
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -978,25 +965,27 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>155</v>
+      </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>28</v>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -1004,7 +993,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1018,18 +1007,18 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1037,27 +1026,27 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>38</v>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1079,19 +1068,11 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1102,27 +1083,27 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>26</v>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1144,19 +1125,15 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr"/>
       <c r="N8" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1167,16 +1144,18 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>155</v>
+      </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="13" t="inlineStr">
@@ -1185,7 +1164,7 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1193,7 +1172,7 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1207,14 +1186,18 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1222,18 +1205,16 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46113</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="13" t="inlineStr">
@@ -1242,7 +1223,7 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1250,7 +1231,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1259,23 +1240,23 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Basketball Shoes Sabrina 3 "What The?"</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1283,17 +1264,17 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
@@ -1303,7 +1284,7 @@
         </is>
       </c>
       <c r="F11" s="14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1320,17 +1301,17 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
@@ -1344,17 +1325,17 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
@@ -1364,7 +1345,7 @@
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1381,15 +1362,19 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -1401,17 +1386,17 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
@@ -1421,7 +1406,7 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1438,15 +1423,19 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -1458,17 +1447,17 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
@@ -1478,7 +1467,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1495,12 +1484,12 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr"/>
@@ -1515,17 +1504,17 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1535,7 +1524,7 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1552,12 +1541,12 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr"/>
@@ -1572,17 +1561,17 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
@@ -1592,7 +1581,7 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1609,12 +1598,12 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr"/>
@@ -1629,17 +1618,17 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
@@ -1649,7 +1638,7 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1666,12 +1655,12 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr"/>
@@ -1686,17 +1675,17 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1706,7 +1695,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1723,15 +1712,19 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr"/>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -1743,17 +1736,17 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1763,7 +1756,7 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1780,15 +1773,19 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr"/>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1800,25 +1797,25 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>24</v>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1840,12 +1837,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr"/>
@@ -1859,7 +1856,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1879,7 +1876,7 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1896,19 +1893,15 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1913,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1940,7 +1933,7 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1957,19 +1950,15 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr"/>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -1981,7 +1970,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2001,7 +1990,7 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
@@ -2018,12 +2007,12 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2038,7 +2027,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2058,7 +2047,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2075,19 +2064,15 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2099,7 +2084,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2119,7 +2104,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2136,19 +2121,15 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr"/>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -2160,7 +2141,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2180,7 +2161,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2197,19 +2178,15 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr"/>
       <c r="N26" s="6" t="inlineStr">
         <is>
@@ -2221,7 +2198,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2241,7 +2218,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2258,19 +2235,15 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr"/>
       <c r="N27" s="6" t="inlineStr">
         <is>
@@ -2282,7 +2255,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2302,7 +2275,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -2319,19 +2292,15 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr"/>
       <c r="N28" s="6" t="inlineStr">
         <is>
@@ -2343,7 +2312,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2353,7 +2322,7 @@
         <v>46113</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
@@ -2363,7 +2332,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2380,15 +2349,19 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr"/>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M29" s="6" t="inlineStr"/>
       <c r="N29" s="6" t="inlineStr">
         <is>
@@ -2400,7 +2373,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2410,7 +2383,7 @@
         <v>46113</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
@@ -2420,7 +2393,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2437,15 +2410,19 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
-        </is>
-      </c>
-      <c r="L30" s="12" t="inlineStr"/>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M30" s="6" t="inlineStr"/>
       <c r="N30" s="6" t="inlineStr">
         <is>
@@ -2457,7 +2434,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2467,7 +2444,7 @@
         <v>46113</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
@@ -2477,7 +2454,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2494,15 +2471,19 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr"/>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -2514,27 +2495,25 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>155</v>
-      </c>
+        <v>46115</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>12</v>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2542,7 +2521,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2556,14 +2535,18 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
-        </is>
-      </c>
-      <c r="L32" s="12" t="inlineStr"/>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O32" s="6" t="n">
@@ -2571,27 +2554,25 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>155</v>
-      </c>
+        <v>46123</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>12</v>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2599,7 +2580,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2608,23 +2589,23 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -2632,828 +2613,10 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-retro-high-og-flight-club-black-and-sail</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr"/>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
-        </is>
-      </c>
-      <c r="Q34" s="12" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
-        <is>
-          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
-        </is>
-      </c>
-      <c r="Q35" s="12" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K36" s="12" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr"/>
-      <c r="M36" s="6" t="inlineStr"/>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
-        </is>
-      </c>
-      <c r="Q36" s="12" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr"/>
-      <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
-        </is>
-      </c>
-      <c r="Q37" s="12" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K38" s="12" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="L38" s="12" t="inlineStr"/>
-      <c r="M38" s="6" t="inlineStr"/>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/order/search</t>
-        </is>
-      </c>
-      <c r="Q38" s="12" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K39" s="12" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
-        </is>
-      </c>
-      <c r="Q39" s="12" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="L40" s="12" t="inlineStr"/>
-      <c r="M40" s="6" t="inlineStr"/>
-      <c r="N40" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
-        </is>
-      </c>
-      <c r="Q40" s="12" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr"/>
-      <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" s="12" t="inlineStr">
-        <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="Q41" s="12" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr"/>
-      <c r="M42" s="6" t="inlineStr"/>
-      <c r="N42" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
-        </is>
-      </c>
-      <c r="Q42" s="12" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar</t>
-        </is>
-      </c>
-      <c r="Q43" s="12" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C44" s="5" t="inlineStr"/>
-      <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr"/>
-      <c r="N44" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="Q44" s="12" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="Q45" s="12" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr"/>
-      <c r="N46" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="Q46" s="12" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="Q47" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3470,13 +2633,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -3528,22 +2691,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3551,29 +2714,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -3581,29 +2744,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -3611,19 +2774,19 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3633,7 +2796,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -3641,29 +2804,29 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -3671,29 +2834,29 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -3701,29 +2864,29 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Jordan CJ1 T-Rexx Green Spark</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -3731,29 +2894,29 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -3761,7 +2924,307 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-28T17:04:52Z</t>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Basketball Shoes Sabrina 3 "What The?"</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:36:22Z</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3786,7 +3249,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="54" customWidth="1" min="11" max="11"/>
@@ -3893,10 +3356,10 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="B2" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3915,32 +3378,28 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -3948,25 +3407,25 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q2" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B3" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3990,19 +3449,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4018,7 +3473,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -4033,14 +3488,14 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4060,23 +3515,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -4084,29 +3539,29 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B5" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4126,19 +3581,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4154,13 +3601,13 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
         <v>59</v>
@@ -4169,14 +3616,14 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B6" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4196,19 +3643,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Jordan Grade School Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4224,13 +3667,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
         <v>59</v>
@@ -4239,10 +3682,10 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4266,19 +3709,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jordan CJ1 T-Rexx Green Spark</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4286,25 +3733,25 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-cj1-t-rexx-green-spark</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -4323,28 +3770,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
+          <t>Basketball Shoes Sabrina 3 "What The?"</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4352,25 +3799,25 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4389,17 +3836,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jordan Retro 3 BOYS TODDLER • WHITE/PINK/GREEN</t>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -4418,13 +3865,13 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4756100.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
         <v>59</v>
@@ -4433,10 +3880,10 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4455,15 +3902,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -4480,13 +3931,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -4495,10 +3946,10 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B11" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -4517,15 +3968,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -4542,13 +3997,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -4557,10 +4012,10 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B12" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4579,12 +4034,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -4604,13 +4059,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -4619,10 +4074,10 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B13" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4641,12 +4096,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -4666,13 +4121,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -4681,10 +4136,10 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B14" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4703,12 +4158,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -4728,13 +4183,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -4743,10 +4198,10 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B15" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4765,12 +4220,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -4790,13 +4245,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -4805,10 +4260,10 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B16" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4827,15 +4282,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
@@ -4852,13 +4311,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -4867,10 +4326,10 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46109</v>
+        <v>46113</v>
       </c>
       <c r="B17" t="n">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4889,15 +4348,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
@@ -4914,13 +4377,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -4929,14 +4392,14 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4956,12 +4419,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -4980,13 +4443,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
         <v>50</v>
@@ -5017,19 +4480,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -5046,13 +4505,13 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>59</v>
@@ -5083,19 +4542,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -5112,13 +4567,13 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
         <v>59</v>
@@ -5149,12 +4604,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -5174,13 +4629,13 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
         <v>59</v>
@@ -5211,19 +4666,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -5240,13 +4691,13 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
         <v>59</v>
@@ -5277,19 +4728,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -5306,13 +4753,13 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -5343,19 +4790,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
@@ -5372,13 +4815,13 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
         <v>59</v>
@@ -5409,19 +4852,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
@@ -5438,13 +4877,13 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>59</v>
@@ -5475,19 +4914,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
@@ -5504,13 +4939,13 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
         <v>59</v>
@@ -5522,7 +4957,7 @@
         <v>46113</v>
       </c>
       <c r="B27" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5541,15 +4976,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
@@ -5566,13 +5005,13 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
         <v>59</v>
@@ -5584,7 +5023,7 @@
         <v>46113</v>
       </c>
       <c r="B28" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5603,15 +5042,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
@@ -5628,13 +5071,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -5646,7 +5089,7 @@
         <v>46113</v>
       </c>
       <c r="B29" t="n">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5665,15 +5108,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -5690,13 +5137,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -5705,14 +5152,14 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B30" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5732,19 +5179,23 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5752,29 +5203,29 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q30" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46113</v>
+        <v>46123</v>
       </c>
       <c r="B31" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5789,28 +5240,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Baby/Toddler Shoes Jordan 1 Retro High OG</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5818,910 +5269,18 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-retro-high-og-flight-club-black-and-sail</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B32" t="n">
-        <v>155</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>59</v>
-      </c>
-      <c r="R32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>50</v>
-      </c>
-      <c r="R33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B34" t="n">
-        <v>155</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>59</v>
-      </c>
-      <c r="R34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B35" t="n">
-        <v>155</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>59</v>
-      </c>
-      <c r="R35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B36" t="n">
-        <v>155</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/order/search</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>59</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B37" t="n">
-        <v>155</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>59</v>
-      </c>
-      <c r="R37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B38" t="n">
-        <v>155</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>59</v>
-      </c>
-      <c r="R38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B39" t="n">
-        <v>155</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>59</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B40" t="n">
-        <v>155</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>59</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>59</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B42" t="n">
-        <v>155</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>59</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B43" t="n">
-        <v>155</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>59</v>
-      </c>
-      <c r="R43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B44" t="n">
-        <v>130</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>59</v>
-      </c>
-      <c r="R44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>50</v>
-      </c>
-      <c r="R45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6895,7 +5454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6914,7 +5473,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  44 releases</t>
+          <t>Next 35 Days  ·  30 releases</t>
         </is>
       </c>
     </row>
@@ -6932,7 +5491,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -6993,7 +5552,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$176</t>
+          <t>$154</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -7050,7 +5609,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -7058,7 +5617,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -7068,7 +5627,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -7082,99 +5641,79 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>WHERE / RELEASE METHOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
+          <t>TOP BRANDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="37" t="inlineStr">
         <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" s="21" t="n"/>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
       <c r="D19" s="21" t="n"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>TOP BRANDS</t>
-        </is>
-      </c>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>████████████</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>█████████</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="n">
-        <v>16</v>
-      </c>
-      <c r="C22" s="40" t="inlineStr">
-        <is>
-          <t>████████████████████</t>
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>█████</t>
         </is>
       </c>
       <c r="D22" s="21" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="n">
-        <v>13</v>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>████████████████</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="B24" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="C24" s="40" t="inlineStr">
-        <is>
-          <t>███████████████</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>████</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
@@ -7197,26 +5736,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>How Scores Work</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>HYPE SCORE  (0–100+)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Brand Tier</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>HIGH brands (Air Jordan, Nike, Yeezy, New Balance, Adidas): +12 pts
 MID brands (Vans, Converse, Puma, Reebok, ASICS, Saucony, Hoka, Salomon): +7 pts
@@ -7225,96 +5764,96 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>Collab</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Any collab keyword (Travis Scott, Off-White, Supreme, Bad Bunny, Kith…): +20 pts</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>Limited / Rare</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Limited, Exclusive, QS, PE, Raffle, Friends &amp; Family, Sample…: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Hot Model</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>Jordan 1–13, Dunk, Air Max, Kobe, Yeezy Boost, Samba, NB 550/990…: +12 pts</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>Retro / Heritage</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Retro, OG, Original, Vintage, Heritage: +4 pts</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>Price Signal</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>Retail ≥ $250 OR retail ≤ $110: +3 pts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>Resale Ratio</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Market ÷ Retail ≥ 2.5×: +35 pts  |  ≥ 2.0×: +28  |  ≥ 1.5×: +18  |  ≥ 1.2×: +8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>Resale Spread</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>Market − Retail ≥ $200: +15 pts  |  ≥ $150: +10  |  ≥ $75: +6  |  ≥ $30: +2</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>Hype Level</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>HIGH ≥ 42 pts     MED ≥ 20 pts     LOW &lt; 20 pts</t>
         </is>
@@ -7322,103 +5861,103 @@
     </row>
     <row r="13" ht="24" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>CONFIDENCE SCORE  (0–100)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>Primary Source</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>Release confirmed by primary scraper (GOAT): +25 pts</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>Secondary Source</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>Confirmed by at least one additional source: +15 pts</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>Retail Price</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>retailPrice field is populated: +15 pts</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>imageUrl field is populated: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>Release URL</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>releaseUrl field is populated: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>Source Count</t>
         </is>
       </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Seen by 3+ sources: +28 pts  |  Seen by 2 sources: +18 pts</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>Single-source cap</t>
         </is>
       </c>
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>Releases seen by only 1 source are capped at 59 (cannot reach HIGH)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="A22" s="45" t="inlineStr">
         <is>
           <t>Confidence Level</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>HIGH ≥ 60 pts     MED ≥ 32 pts     LOW &lt; 32 pts</t>
         </is>
@@ -7426,43 +5965,43 @@
     </row>
     <row r="23" ht="24" customHeight="1"/>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>PRIORITY</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="47" t="inlineStr">
+      <c r="A25" s="46" t="inlineStr">
         <is>
           <t>Must Watch</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>Hype = HIGH  AND  Confidence = HIGH</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>Hype = HIGH + Confidence = MED, OR Hype = MED + Confidence = HIGH</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>Low Priority</t>
         </is>
       </c>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>All other hype / confidence combinations</t>
         </is>
@@ -7470,43 +6009,43 @@
     </row>
     <row r="28" ht="24" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="42" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>FLIP SCORE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>Flip % = round((Market Value − Retail Price) / Retail Price × 100)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>$150 retail, $225 market  →  Flip % = +50%  (50% above retail)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>No value</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>Shown as blank when retail or market value is missing</t>
         </is>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -2701,17 +2701,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2753,36 +2753,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-29T17:05:57Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -917,7 +917,7 @@
         <v>46113</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>46113</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -1010,14 +1010,10 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr"/>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -1029,7 +1025,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -1039,7 +1035,7 @@
         <v>46113</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
@@ -1049,7 +1045,7 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1071,10 +1067,14 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr"/>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
         <v>46113</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
         <v>46113</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/61059860.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1218,17 +1218,17 @@
         <v>46113</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>17</v>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>46113</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>46113</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46113</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46113</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>46113</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>46113</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46113</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46113</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>46113</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>46113</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>46113</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>46113</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46113</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>46113</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>46113</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>46113</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>46113</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2753,6 +2753,972 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:38:18Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3919,7 @@
         <v>46113</v>
       </c>
       <c r="B3" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3007,7 +3973,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q3" t="n">
         <v>59</v>
@@ -3019,7 +3985,7 @@
         <v>46113</v>
       </c>
       <c r="B4" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3043,14 +4009,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jordan Grade School Retro 3 GIRLS GRADE SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -3067,13 +4029,13 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/62059960.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
         <v>59</v>
@@ -3085,7 +4047,7 @@
         <v>46113</v>
       </c>
       <c r="B5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3109,10 +4071,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
@@ -3129,13 +4095,13 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="n">
         <v>59</v>
@@ -3147,7 +4113,7 @@
         <v>46113</v>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3171,12 +4137,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -3195,13 +4161,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q6" t="n">
         <v>59</v>
@@ -3213,7 +4179,7 @@
         <v>46113</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3237,12 +4203,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -3261,13 +4227,13 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/61059860.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q7" t="n">
         <v>59</v>
@@ -3279,11 +4245,11 @@
         <v>46113</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3337,7 +4303,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
         <v>59</v>
@@ -3415,7 +4381,7 @@
         <v>46113</v>
       </c>
       <c r="B10" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3469,7 +4435,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -3481,7 +4447,7 @@
         <v>46113</v>
       </c>
       <c r="B11" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3535,7 +4501,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -3547,7 +4513,7 @@
         <v>46113</v>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3601,7 +4567,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -3737,7 +4703,7 @@
         <v>46113</v>
       </c>
       <c r="B15" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3787,7 +4753,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -3799,7 +4765,7 @@
         <v>46113</v>
       </c>
       <c r="B16" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3849,7 +4815,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -3861,7 +4827,7 @@
         <v>46113</v>
       </c>
       <c r="B17" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3915,7 +4881,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -3927,7 +4893,7 @@
         <v>46113</v>
       </c>
       <c r="B18" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3981,7 +4947,7 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -4059,7 +5025,7 @@
         <v>46113</v>
       </c>
       <c r="B20" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4109,7 +5075,7 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
         <v>59</v>
@@ -4121,7 +5087,7 @@
         <v>46113</v>
       </c>
       <c r="B21" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4171,7 +5137,7 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
         <v>59</v>
@@ -4183,7 +5149,7 @@
         <v>46113</v>
       </c>
       <c r="B22" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -4233,7 +5199,7 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
         <v>59</v>
@@ -4245,7 +5211,7 @@
         <v>46113</v>
       </c>
       <c r="B23" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -4295,7 +5261,7 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -4307,7 +5273,7 @@
         <v>46113</v>
       </c>
       <c r="B24" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4357,7 +5323,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
         <v>59</v>
@@ -4369,7 +5335,7 @@
         <v>46113</v>
       </c>
       <c r="B25" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4419,7 +5385,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
         <v>59</v>
@@ -4431,7 +5397,7 @@
         <v>46113</v>
       </c>
       <c r="B26" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4481,7 +5447,7 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
         <v>59</v>
@@ -4493,7 +5459,7 @@
         <v>46113</v>
       </c>
       <c r="B27" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4543,7 +5509,7 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
         <v>59</v>
@@ -4555,7 +5521,7 @@
         <v>46113</v>
       </c>
       <c r="B28" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4609,7 +5575,7 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -4621,7 +5587,7 @@
         <v>46113</v>
       </c>
       <c r="B29" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4675,7 +5641,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -5150,7 +6116,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$154</t>
+          <t>$87</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -5207,7 +6173,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -5225,7 +6191,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
         <v>46113</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
+          <t>adidas Anthony Edwards 2 BOYS GRADE SCHOOL • YELLOW/PURPLE/BLUE</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
@@ -968,7 +968,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/62009505.html</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
@@ -978,17 +978,17 @@
         <v>46113</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>15</v>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -1010,10 +1010,14 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr"/>
+          <t>Jordan 1 Retro High OG FC BOYS PRE-SCHOOL • BLACK/SAIL/RED</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -1025,7 +1029,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/I9926001.html</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -1035,7 +1039,7 @@
         <v>46113</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
@@ -1067,12 +1071,12 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -1096,7 +1100,7 @@
         <v>46113</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
@@ -1106,7 +1110,7 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1128,14 +1132,10 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr"/>
       <c r="N8" s="6" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
         <v>46113</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/61059860.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1218,17 +1218,17 @@
         <v>46113</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>20</v>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>19</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1245,24 +1245,20 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
+          <t>Jordan Retro 1 High OG BOYS GRADE SCHOOL • BLACK/RED/WHITE</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1273,7 +1269,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19839C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62992701.html</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -1282,7 +1278,9 @@
       <c r="A11" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>95</v>
+      </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="13" t="inlineStr">
@@ -1291,7 +1289,7 @@
         </is>
       </c>
       <c r="F11" s="14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1299,7 +1297,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1308,23 +1306,23 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Basketball Shoes Sabrina 3 "What The?"</t>
+          <t>Jordan Retro 4 GIRLS PRE-SCHOOL • PINKSICLE/COCONUT MILK/BLACK</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1332,7 +1330,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/IB6715.html</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -1342,7 +1340,7 @@
         <v>46113</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
@@ -1352,7 +1350,7 @@
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1369,17 +1367,17 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+          <t>Jordan Retro 4 GIRLS TODDLER • PINKSICLE/COCONUT MILK/ANTHRACITE</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr"/>
@@ -1393,7 +1391,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/IB6714.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1403,7 +1401,7 @@
         <v>46113</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
@@ -1413,7 +1411,7 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1430,17 +1428,17 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
@@ -1454,7 +1452,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1464,7 +1462,7 @@
         <v>46113</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
@@ -1474,7 +1472,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1491,17 +1489,17 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr"/>
@@ -1515,7 +1513,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/61059860.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1525,17 +1523,17 @@
         <v>46113</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>12</v>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1552,16 +1550,24 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1572,7 +1578,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19839C.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -1581,9 +1587,7 @@
       <c r="A16" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>150</v>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="13" t="inlineStr">
@@ -1600,7 +1604,7 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1614,14 +1618,18 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr"/>
+          <t>Basketball Shoes Sabrina 3 "What The?"</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1629,7 +1637,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1639,7 +1647,7 @@
         <v>46113</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
@@ -1671,10 +1679,14 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="inlineStr"/>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -1686,7 +1698,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1696,7 +1708,7 @@
         <v>46113</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1728,10 +1740,14 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -1743,7 +1759,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1753,7 +1769,7 @@
         <v>46113</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1785,12 +1801,12 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
@@ -1804,7 +1820,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1814,7 +1830,7 @@
         <v>46113</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1824,7 +1840,7 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1846,14 +1862,10 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -1865,7 +1877,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1874,7 +1886,9 @@
       <c r="A21" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="13" t="inlineStr">
@@ -1891,7 +1905,7 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
@@ -1905,18 +1919,14 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O21" s="6" t="n">
@@ -1924,7 +1934,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1934,7 +1944,7 @@
         <v>46113</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1944,7 +1954,7 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1961,12 +1971,12 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr"/>
@@ -1981,7 +1991,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -1991,7 +2001,7 @@
         <v>46113</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
@@ -2001,7 +2011,7 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
@@ -2018,12 +2028,12 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -2038,7 +2048,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2048,7 +2058,7 @@
         <v>46113</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
@@ -2058,7 +2068,7 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2075,15 +2085,19 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr"/>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2095,7 +2109,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2105,7 +2119,7 @@
         <v>46113</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
@@ -2115,7 +2129,7 @@
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2132,15 +2146,19 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr"/>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="inlineStr"/>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -2152,7 +2170,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2161,9 +2179,7 @@
       <c r="A26" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>80</v>
-      </c>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
@@ -2172,7 +2188,7 @@
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2180,7 +2196,7 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2189,19 +2205,23 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr"/>
+          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="M26" s="6" t="inlineStr"/>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O26" s="6" t="n">
@@ -2209,7 +2229,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2219,7 +2239,7 @@
         <v>46113</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
@@ -2251,7 +2271,7 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr"/>
@@ -2266,7 +2286,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2276,7 +2296,7 @@
         <v>46113</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
@@ -2308,7 +2328,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr"/>
@@ -2323,7 +2343,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2333,7 +2353,7 @@
         <v>46113</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
@@ -2365,7 +2385,7 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr"/>
@@ -2380,7 +2400,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2390,7 +2410,7 @@
         <v>46113</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
@@ -2400,7 +2420,7 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2417,19 +2437,15 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L30" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr"/>
       <c r="M30" s="6" t="inlineStr"/>
       <c r="N30" s="6" t="inlineStr">
         <is>
@@ -2441,7 +2457,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2451,7 +2467,7 @@
         <v>46113</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
@@ -2461,7 +2477,7 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2478,19 +2494,15 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -2502,7 +2514,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2512,7 +2524,7 @@
         <v>46113</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
@@ -2522,7 +2534,7 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2539,19 +2551,15 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L32" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
@@ -2563,25 +2571,27 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>95</v>
+      </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>24</v>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>6</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2589,7 +2599,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2598,23 +2608,19 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -2622,25 +2628,27 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46123</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>95</v>
+      </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>28</v>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>6</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2648,7 +2656,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2657,23 +2665,19 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 1 Retro High OG</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O34" s="6" t="n">
@@ -2681,10 +2685,311 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="Q34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K35" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K36" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K37" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="Q37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr"/>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K38" s="12" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr"/>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="Q38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K39" s="12" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" s="12" t="inlineStr">
+        <is>
           <t>https://www.nike.com/launch/t/air-jordan-1-retro-high-og-flight-club-black-and-sail</t>
         </is>
       </c>
-      <c r="Q34" s="12" t="inlineStr"/>
+      <c r="Q39" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2701,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2759,7 +3064,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RETAIL_CHANGED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2769,39 +3074,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>adidas Anthony Edwards 2 BOYS GRADE SCHOOL • YELLOW/PURPLE/BLUE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RETAIL_CHANGED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2811,39 +3104,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>Jordan 1 Retro High OG FC BOYS PRE-SCHOOL • BLACK/SAIL/RED</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RETAIL_CHANGED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2858,34 +3139,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>Jordan Retro 1 High OG BOYS GRADE SCHOOL • BLACK/RED/WHITE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RETAIL_CHANGED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2900,34 +3169,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>Jordan Retro 4 GIRLS PRE-SCHOOL • PINKSICLE/COCONUT MILK/BLACK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RETAIL_CHANGED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2942,27 +3199,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>Jordan Retro 4 GIRLS TODDLER • PINKSICLE/COCONUT MILK/ANTHRACITE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -2979,12 +3224,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2994,17 +3239,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3266,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
+          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3036,17 +3281,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3308,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3078,17 +3323,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3350,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3120,17 +3365,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3392,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3162,17 +3407,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3434,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3204,17 +3449,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3476,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3246,17 +3491,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3518,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3288,17 +3533,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3565,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3330,17 +3575,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3607,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3372,17 +3617,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3644,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3414,17 +3659,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3441,12 +3686,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3456,17 +3701,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3728,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3498,17 +3743,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3525,12 +3770,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3540,17 +3785,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3812,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3582,17 +3827,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3859,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3624,17 +3869,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3651,12 +3896,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3666,17 +3911,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-30T19:38:18Z</t>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3693,32 +3938,242 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:59:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:59:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:59:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:59:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Vans</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:59:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>retailPrice</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-30T19:38:18Z</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:59:25Z</t>
         </is>
       </c>
     </row>
@@ -3733,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3919,7 +4374,7 @@
         <v>46113</v>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3938,17 +4393,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
+          <t>adidas Anthony Edwards 2 BOYS GRADE SCHOOL • YELLOW/PURPLE/BLUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -3967,13 +4422,13 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/62009505.html</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
         <v>59</v>
@@ -3985,11 +4440,11 @@
         <v>46113</v>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4009,10 +4464,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Jordan 1 Retro High OG FC BOYS PRE-SCHOOL • BLACK/SAIL/RED</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -4029,13 +4488,13 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/I9926001.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
         <v>59</v>
@@ -4047,7 +4506,7 @@
         <v>46113</v>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4071,12 +4530,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
+          <t>Jordan AJ 1 Retro High OG FC MENS • BLACK/UNIVERSITY RED/SAIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4095,7 +4554,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/9811001.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -4113,7 +4572,7 @@
         <v>46113</v>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4137,14 +4596,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Jordan Luka 5 MENS • BLACK/WHITE/GREY</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -4161,13 +4616,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/V8082003.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
         <v>59</v>
@@ -4179,7 +4634,7 @@
         <v>46113</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4203,7 +4658,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
+          <t>Jordan Pre-School Retro 3 GIRLS PRE-SCHOOL • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4227,7 +4682,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/61059860.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/64059760.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -4245,11 +4700,11 @@
         <v>46113</v>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4264,24 +4719,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
+          <t>Jordan Retro 1 High OG BOYS GRADE SCHOOL • BLACK/RED/WHITE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>exclusive, kids</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4297,13 +4748,13 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19839C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/62992701.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
         <v>59</v>
@@ -4315,7 +4766,7 @@
         <v>46113</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4334,28 +4785,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Basketball Shoes Sabrina 3 "What The?"</t>
+          <t>Jordan Retro 4 GIRLS PRE-SCHOOL • PINKSICLE/COCONUT MILK/BLACK</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4363,16 +4814,16 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/IB6715.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
@@ -4381,7 +4832,7 @@
         <v>46113</v>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4400,17 +4851,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+          <t>Jordan Retro 4 GIRLS TODDLER • PINKSICLE/COCONUT MILK/ANTHRACITE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -4429,13 +4880,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/IB6714.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -4447,7 +4898,7 @@
         <v>46113</v>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -4466,17 +4917,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -4495,13 +4946,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -4513,7 +4964,7 @@
         <v>46113</v>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4532,17 +4983,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
+          <t>Jordan Toddler Retro 3 GIRLS TODDLER • PINK/ORANGE/BLUE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -4561,13 +5012,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/61059860.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -4579,11 +5030,11 @@
         <v>46113</v>
       </c>
       <c r="B13" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4598,16 +5049,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>ENTRIES OPEN App Entry Converse Grade School SHAI 001 Camo BOYS GRADE SCHOOL • GREEN/BROWN</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4623,13 +5082,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19839C.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -4641,7 +5100,7 @@
         <v>46113</v>
       </c>
       <c r="B14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4665,19 +5124,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Basketball Shoes Sabrina 3 "What The?"</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -4685,7 +5148,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -4694,7 +5157,7 @@
         <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R14" t="inlineStr"/>
     </row>
@@ -4703,7 +5166,7 @@
         <v>46113</v>
       </c>
       <c r="B15" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4727,10 +5190,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHRE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
@@ -4747,7 +5214,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2627.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -4765,7 +5232,7 @@
         <v>46113</v>
       </c>
       <c r="B16" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4789,10 +5256,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Nike Ja 3 JP BOYS GRADE SCHOOL • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
@@ -4809,7 +5280,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV26203.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -4827,7 +5298,7 @@
         <v>46113</v>
       </c>
       <c r="B17" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4851,12 +5322,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+          <t>Nike Ja 3 JP BOYS PRE-SCHOOL • ARNTHRACITE/BRIGHT CRIMSON</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -4875,7 +5346,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV2620.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -4893,7 +5364,7 @@
         <v>46113</v>
       </c>
       <c r="B18" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4917,14 +5388,10 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike JA 3 MENS • ANTHRACITE/BRIGHT CRIMSON/YELLOW OCHER</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -4941,13 +5408,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240001.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -4959,7 +5426,7 @@
         <v>46113</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4983,23 +5450,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike JA 3 MENS • GREEN SPARK/BLACK/UNIVERSITY RED</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -5007,7 +5470,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
+          <t>https://www.footlocker.com/release-calendar/nike/U7240300.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -5016,7 +5479,7 @@
         <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R19" t="inlineStr"/>
     </row>
@@ -5025,7 +5488,7 @@
         <v>46113</v>
       </c>
       <c r="B20" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -5044,12 +5507,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -5069,13 +5532,13 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q20" t="n">
         <v>59</v>
@@ -5087,7 +5550,7 @@
         <v>46113</v>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -5106,12 +5569,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Nike Mind 002 MENS • BLUE/PLATINUM/BLUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -5131,13 +5594,13 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4308400.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
         <v>59</v>
@@ -5149,7 +5612,7 @@
         <v>46113</v>
       </c>
       <c r="B22" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5168,15 +5631,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Nike Sabrina 3 GIRLS GRADE SCHOOL • IGLOO/HOT LAVA/BLUE CRYSTAL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>basketball, kids</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -5193,13 +5660,13 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R3208300.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q22" t="n">
         <v>59</v>
@@ -5211,7 +5678,7 @@
         <v>46113</v>
       </c>
       <c r="B23" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5230,15 +5697,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Nike Zoom Huarache 2K4 OT MENS • BLACK/BLACK</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -5255,13 +5726,13 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IV329001.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -5273,7 +5744,7 @@
         <v>46113</v>
       </c>
       <c r="B24" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5292,24 +5763,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Sabrina 3 "What The?" Igloo and Blue Crystal</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5317,16 +5792,16 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.nike.com/launch/t/sabrina-3-what-the-igloo-and-blue-crystal</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R24" t="inlineStr"/>
     </row>
@@ -5335,7 +5810,7 @@
         <v>46113</v>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5359,7 +5834,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -5379,7 +5854,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -5397,7 +5872,7 @@
         <v>46113</v>
       </c>
       <c r="B26" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -5421,7 +5896,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -5441,7 +5916,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -5459,7 +5934,7 @@
         <v>46113</v>
       </c>
       <c r="B27" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5483,7 +5958,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -5503,7 +5978,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -5521,7 +5996,7 @@
         <v>46113</v>
       </c>
       <c r="B28" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5540,19 +6015,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
@@ -5569,13 +6040,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -5587,7 +6058,7 @@
         <v>46113</v>
       </c>
       <c r="B29" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5606,19 +6077,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -5635,13 +6102,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -5653,7 +6120,7 @@
         <v>46113</v>
       </c>
       <c r="B30" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5672,19 +6139,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
@@ -5701,13 +6164,13 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
         <v>59</v>
@@ -5716,14 +6179,14 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5738,28 +6201,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5767,29 +6226,29 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46123</v>
+        <v>46113</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5804,28 +6263,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 1 Retro High OG</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -5833,18 +6288,348 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-retro-high-og-flight-club-black-and-sail</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>59</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>59</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>59</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B35" t="n">
+        <v>130</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>59</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>50</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-1-retro-high-og-flight-club-black-and-sail</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>28</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q37" t="n">
         <v>50</v>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6018,7 +6803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6037,7 +6822,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  31 releases</t>
+          <t>Next 35 Days  ·  36 releases</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6840,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -6116,7 +6901,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$87</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -6173,7 +6958,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -6181,7 +6966,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -6191,7 +6976,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -6247,15 +7032,15 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>████████████</t>
+          <t>███████████████</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>
@@ -6263,15 +7048,15 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B24" s="39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>█████████</t>
+          <t>████████████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -6295,7 +7080,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
    